--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.673.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.673.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="2010">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="2010">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240411000000</t>
+    <t>20241029000000</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>retired</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,13 +63,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T01:00:00+02:00</t>
+    <t>2024-10-29T00:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+    <t>Agence du Numérique en Santé(ANS) -2 - 10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Description</t>
@@ -93,217 +93,217 @@
     <t>10326007</t>
   </si>
   <si>
-    <t>Coronary artery bypass with autogenous graft, three grafts</t>
+    <t>triple pontage coronarien par autogreffe</t>
   </si>
   <si>
     <t>10458001</t>
   </si>
   <si>
-    <t>Evacuation of intracerebral hematoma</t>
+    <t>évacuation d'un hématome intracérébral</t>
   </si>
   <si>
     <t>105373008</t>
   </si>
   <si>
-    <t>Percutaneous insertion of intravascular filter</t>
+    <t>insertion percutanée d'un filtre intravasculaire</t>
   </si>
   <si>
     <t>107907001</t>
   </si>
   <si>
-    <t>Operative procedure on digestive system</t>
+    <t>intervention chirurgicale sur l'appareil digestif</t>
   </si>
   <si>
     <t>107938000</t>
   </si>
   <si>
-    <t>Small intestine excision</t>
+    <t>excision de l'intestin grêle</t>
   </si>
   <si>
     <t>107963000</t>
   </si>
   <si>
-    <t>Liver excision</t>
+    <t>hépatectomie</t>
   </si>
   <si>
     <t>108021004</t>
   </si>
   <si>
-    <t>Operative procedure on male genitourinary system</t>
+    <t>intervention chirurgicale du système urogénital</t>
   </si>
   <si>
     <t>108022006</t>
   </si>
   <si>
-    <t>Kidney excision</t>
+    <t>excision au niveau du rein</t>
   </si>
   <si>
     <t>108034003</t>
   </si>
   <si>
-    <t>Bladder excision</t>
+    <t>cystectomie</t>
   </si>
   <si>
     <t>10847001</t>
   </si>
   <si>
-    <t>Bronchoscopy</t>
+    <t>endoscopie bronchique</t>
   </si>
   <si>
     <t>11050006</t>
   </si>
   <si>
-    <t>Closure of vesicouterine fistula with hysterectomy</t>
+    <t>fermeture de fistule vésico-utérine avec hystérectomie</t>
   </si>
   <si>
     <t>11101003</t>
   </si>
   <si>
-    <t>Percutaneous transluminal coronary angioplasty</t>
+    <t>angioplastie coronarienne transluminale percutanée</t>
   </si>
   <si>
     <t>112695004</t>
   </si>
   <si>
-    <t>Closure</t>
+    <t>fermeture</t>
   </si>
   <si>
     <t>112698002</t>
   </si>
   <si>
-    <t>Operation on joint</t>
+    <t>intervention chirurgicale d'une articulation</t>
   </si>
   <si>
     <t>112727005</t>
   </si>
   <si>
-    <t>Revision of hip replacement</t>
+    <t>reprise de prothèse de la hanche</t>
   </si>
   <si>
     <t>112746006</t>
   </si>
   <si>
-    <t>Operative procedure on hand</t>
+    <t>intervention chirurgicale sur la main</t>
   </si>
   <si>
     <t>112788002</t>
   </si>
   <si>
-    <t>Operation on accessory sinus</t>
+    <t>intervention chirurgicale sur un sinus paranasal</t>
   </si>
   <si>
     <t>112802009</t>
   </si>
   <si>
-    <t>Cardiovascular surgical procedure</t>
+    <t>intervention chirurgicale cardiovasculaire</t>
   </si>
   <si>
     <t>112811009</t>
   </si>
   <si>
-    <t>Atrioseptoplasty</t>
-  </si>
-  <si>
-    <t>112816004</t>
-  </si>
-  <si>
-    <t>Valvuloplasty of aortic valve</t>
+    <t>fermeture d'une communication interatriale</t>
+  </si>
+  <si>
+    <t>232834008</t>
+  </si>
+  <si>
+    <t>valvuloplastie aortique par ballonnet</t>
   </si>
   <si>
     <t>112828007</t>
   </si>
   <si>
-    <t>Femoral-popliteal artery bypass graft</t>
+    <t>pontage fémoropoplité</t>
   </si>
   <si>
     <t>11401008</t>
   </si>
   <si>
-    <t>Dilation and curettage of uterus</t>
+    <t>dilatation et curetage de l'utérus</t>
   </si>
   <si>
     <t>11466000</t>
   </si>
   <si>
-    <t>Cesarean section</t>
+    <t>césarienne</t>
   </si>
   <si>
     <t>116028008</t>
   </si>
   <si>
-    <t>Salpingo-oophorectomy</t>
+    <t>salpingo-ovariectomie</t>
   </si>
   <si>
     <t>116141005</t>
   </si>
   <si>
-    <t>Abdominal hysterectomy</t>
+    <t>hystérectomie abdominale</t>
   </si>
   <si>
     <t>116143008</t>
   </si>
   <si>
-    <t>Total abdominal hysterectomy</t>
+    <t>hystérectomie totale par voie abdominale</t>
   </si>
   <si>
     <t>116144002</t>
   </si>
   <si>
-    <t>Total abdominal hysterectomy with bilateral salpingo-oophorectomy</t>
+    <t>hystérectomie totale avec salpingo-oophorectomie bilatérale par voie abdominale</t>
   </si>
   <si>
     <t>116241004</t>
   </si>
   <si>
-    <t>Pancreaticoduodenectomy</t>
+    <t>duodénopancréatectomie</t>
   </si>
   <si>
     <t>118470002</t>
   </si>
   <si>
-    <t>Internal skeletal fixation</t>
+    <t>fixation squelettique interne</t>
   </si>
   <si>
     <t>118675001</t>
   </si>
   <si>
-    <t>Procedure on female genital system</t>
+    <t>procédure du système génital fémininm</t>
   </si>
   <si>
     <t>118683007</t>
   </si>
   <si>
-    <t>Procedure on ear and related structures</t>
+    <t>procédure sur le système auditif</t>
   </si>
   <si>
     <t>118716003</t>
   </si>
   <si>
-    <t>Procedure on foot</t>
+    <t>procédure sur le pied</t>
   </si>
   <si>
     <t>118795000</t>
   </si>
   <si>
-    <t>Procedure on pleura</t>
+    <t>procédure sur la plèvre</t>
   </si>
   <si>
     <t>118804001</t>
   </si>
   <si>
-    <t>Procedure on blood vessel</t>
+    <t>procédure sur un vaisseau sanguin</t>
   </si>
   <si>
     <t>118831003</t>
   </si>
   <si>
-    <t>Procedure on intestine</t>
+    <t>procédure sur les intestins</t>
   </si>
   <si>
     <t>118949002</t>
   </si>
   <si>
-    <t>Procedure on extremity</t>
+    <t>procédure sur un membre</t>
   </si>
   <si>
     <t>118950002</t>
@@ -315,451 +315,451 @@
     <t>118955007</t>
   </si>
   <si>
-    <t>Implantation to cardiovascular system</t>
+    <t>implantation dans le système cardiovasculaire</t>
   </si>
   <si>
     <t>119283008</t>
   </si>
   <si>
-    <t>Open biopsy</t>
+    <t>biopsie ouverte</t>
   </si>
   <si>
     <t>119614000</t>
   </si>
   <si>
-    <t>Hip joint reconstruction</t>
+    <t>reconstruction de l'articulation de la hanche</t>
   </si>
   <si>
     <t>119762001</t>
   </si>
   <si>
-    <t>Cardiovascular system transplantation</t>
+    <t>transplantation du système cardiovasculaire</t>
   </si>
   <si>
     <t>119922005</t>
   </si>
   <si>
-    <t>Biliary tract endoscopy</t>
+    <t>endoscopie de la vésicule biliaire et/ou de l'arbre biliaire</t>
   </si>
   <si>
     <t>119954001</t>
   </si>
   <si>
-    <t>Adenoid excision</t>
+    <t>adénoïdectomie</t>
   </si>
   <si>
     <t>120001005</t>
   </si>
   <si>
-    <t>Testis excision</t>
+    <t>résection au niveau du testicule</t>
   </si>
   <si>
     <t>12132004</t>
   </si>
   <si>
-    <t>Langenbeck operation, cleft palate repair</t>
+    <t>opération de Langenbeck, réparation d'une fente palatine</t>
   </si>
   <si>
     <t>122459003</t>
   </si>
   <si>
-    <t>Dissection procedure</t>
+    <t>intervention chirurgicale de dissection</t>
   </si>
   <si>
     <t>122465003</t>
   </si>
   <si>
-    <t>Reconstruction procedure</t>
+    <t>chirurgie de reconstruction</t>
   </si>
   <si>
     <t>122470005</t>
   </si>
   <si>
-    <t>Reduction of closed fracture</t>
+    <t>réduction d'une fracture fermée</t>
   </si>
   <si>
     <t>122471009</t>
   </si>
   <si>
-    <t>Reduction of open fracture</t>
+    <t>réduction d'une fracture ouverte</t>
   </si>
   <si>
     <t>12398007</t>
   </si>
   <si>
-    <t>Excision of endometrial synechiae</t>
+    <t>résection de synéchies endométriales</t>
   </si>
   <si>
     <t>125571002</t>
   </si>
   <si>
-    <t>Lobectomy</t>
+    <t>lobectomie</t>
   </si>
   <si>
     <t>12658000</t>
   </si>
   <si>
-    <t>Operation on female genital organs</t>
+    <t>intervention chirurgicale des organes génitaux féminins</t>
   </si>
   <si>
     <t>12660003</t>
   </si>
   <si>
-    <t>Repair of complete shoulder cuff avulsion, chronic</t>
+    <t>réparation d'une avulsion complète chronique de la coiffe des rotateurs</t>
   </si>
   <si>
     <t>127601009</t>
   </si>
   <si>
-    <t>Hammer toe operation</t>
+    <t>intervention chirurgicale sur un orteil en marteau</t>
   </si>
   <si>
     <t>12826007</t>
   </si>
   <si>
-    <t>Dorrance operation, push-back operation for cleft palate</t>
+    <t>opération de Dorrance, fermeture d'une fente palatine par push-back</t>
   </si>
   <si>
     <t>128952006</t>
   </si>
   <si>
-    <t>Catheterization of both left and right heart with graft</t>
+    <t>cathétérisme cardiaque droit et gauche avec greffe</t>
   </si>
   <si>
     <t>129252005</t>
   </si>
   <si>
-    <t>Suprapubic cystostomy</t>
+    <t>cystostomie sus-pubienne</t>
   </si>
   <si>
     <t>13091001</t>
   </si>
   <si>
-    <t>Dilation and curettage</t>
+    <t>dilatation et curetage</t>
   </si>
   <si>
     <t>13254001</t>
   </si>
   <si>
-    <t>Abdominal hysterectomy with colpo-urethrocystopexy, Marshall-Marchetti-Krantz type</t>
+    <t>hystérectomie abdominale avec colpo-urétrocystopexie, type Marshall-Marchetti-Krantz</t>
   </si>
   <si>
     <t>133864008</t>
   </si>
   <si>
-    <t>Lithotripsy</t>
+    <t>lithotripsie</t>
   </si>
   <si>
     <t>13529000</t>
   </si>
   <si>
-    <t>Nasal septoplasty</t>
+    <t>septoplastie nasale</t>
   </si>
   <si>
     <t>13619001</t>
   </si>
   <si>
-    <t>Thyroidectomy</t>
+    <t>thyroïdectomie</t>
   </si>
   <si>
     <t>13662000</t>
   </si>
   <si>
-    <t>Anastomosis of pulmonary-subclavian artery by Blalock-Taussig operation</t>
+    <t>anastomose de Blalock-Tausing entre l'artère sous-clavière et l'artère pulmonaire</t>
   </si>
   <si>
     <t>13793006</t>
   </si>
   <si>
-    <t>Extracapsular extraction of lens</t>
+    <t>extraction extracapsulaire du cristallin</t>
   </si>
   <si>
     <t>13910004</t>
   </si>
   <si>
-    <t>Combined anteroposterior colporrhaphy</t>
+    <t>colporraphie antéropostérieure combinée</t>
   </si>
   <si>
     <t>150062003</t>
   </si>
   <si>
-    <t>Osteotomy</t>
+    <t>ostéotomie</t>
   </si>
   <si>
     <t>15018006</t>
   </si>
   <si>
-    <t>Laparoscopic repair of inguinal hernia</t>
+    <t>réparation laparoscopique d'une hernie inguinale</t>
   </si>
   <si>
     <t>15023006</t>
   </si>
   <si>
-    <t>Thromboendarterectomy with graft of carotid artery by neck incision</t>
+    <t>thromboendartériectomie avec greffe de la carotide par incision du cou</t>
   </si>
   <si>
     <t>15413009</t>
   </si>
   <si>
-    <t>High forceps delivery with episiotomy</t>
+    <t>accouchement avec forceps haut avec épisiotomie</t>
   </si>
   <si>
     <t>15617002</t>
   </si>
   <si>
-    <t>Ligation of varicose vein of lower limb</t>
+    <t>ligature d'une varice du membre inférieur</t>
   </si>
   <si>
     <t>16545005</t>
   </si>
   <si>
-    <t>Operation on nervous system</t>
+    <t>intervention chirurgicale sur le système nerveux</t>
   </si>
   <si>
     <t>16564004</t>
   </si>
   <si>
-    <t>Hartmann operation, rectal resection</t>
+    <t>résection du rectum selon Hartmann</t>
   </si>
   <si>
     <t>172043006</t>
   </si>
   <si>
-    <t>Simple mastectomy</t>
+    <t>mastectomie simple</t>
   </si>
   <si>
     <t>172049005</t>
   </si>
   <si>
-    <t>Quadrantectomy of breast</t>
+    <t>quadrantectomie du sein</t>
   </si>
   <si>
     <t>172132001</t>
   </si>
   <si>
-    <t>Enucleation of eyeball</t>
+    <t>énucléation du bulbe d'un œil</t>
   </si>
   <si>
     <t>172485001</t>
   </si>
   <si>
-    <t>Laser trabeculoplasty</t>
+    <t>trabéculoplastie au laser</t>
   </si>
   <si>
     <t>172523009</t>
   </si>
   <si>
-    <t>Intracapsular extraction of lens</t>
+    <t>extraction intracapsulaire du cristallin</t>
   </si>
   <si>
     <t>172524003</t>
   </si>
   <si>
-    <t>Forceps extraction of lens</t>
+    <t>extraction du cristallin à l'aide d'une pince</t>
   </si>
   <si>
     <t>172532006</t>
   </si>
   <si>
-    <t>YAG laser capsulotomy of lens</t>
+    <t>capsulotomie du cristallin par laser YAG</t>
   </si>
   <si>
     <t>172676009</t>
   </si>
   <si>
-    <t>Myringotomy and insertion of short-term tympanic ventilation tube</t>
+    <t>myringotomie et insertion d'un aérateur trans-tympanique à court terme</t>
   </si>
   <si>
     <t>172679002</t>
   </si>
   <si>
-    <t>Myringotomy and insertion of T tube</t>
+    <t>myringotomie et mise en place d'un drain en T</t>
   </si>
   <si>
     <t>172732009</t>
   </si>
   <si>
-    <t>Implantation of intracochlear prosthesis</t>
+    <t>pose d'un implant intracochléaire</t>
   </si>
   <si>
     <t>172790004</t>
   </si>
   <si>
-    <t>Submucous resection of nasal septum</t>
+    <t>résection sous-muqueuse de la cloison nasale</t>
   </si>
   <si>
     <t>172805009</t>
   </si>
   <si>
-    <t>Cauterization of nasal turbinate</t>
+    <t>turbinoplastie</t>
   </si>
   <si>
     <t>172812000</t>
   </si>
   <si>
-    <t>Cauterization of internal nose</t>
+    <t>cautérisation endonasale</t>
   </si>
   <si>
     <t>172825008</t>
   </si>
   <si>
-    <t>Nasal polypectomy</t>
+    <t>polypectomie nasale</t>
   </si>
   <si>
     <t>17293009</t>
   </si>
   <si>
-    <t>Bilateral segmental vasectomy and ligation</t>
+    <t>excision et ligature segmentaires bilatérales des canaux déférents</t>
   </si>
   <si>
     <t>173171007</t>
   </si>
   <si>
-    <t>Lobectomy of lung</t>
+    <t>lobectomie d'un poumon</t>
   </si>
   <si>
     <t>173422009</t>
   </si>
   <si>
-    <t>Tonsillectomy</t>
+    <t>amygdalectomie</t>
   </si>
   <si>
     <t>173747005</t>
   </si>
   <si>
-    <t>Roux-en-Y gastrojejunostomy</t>
+    <t>gastrojéjunostomie avec anse en Y de Roux</t>
   </si>
   <si>
     <t>173977007</t>
   </si>
   <si>
-    <t>Creation of ileostomy</t>
+    <t>création d'une iléostomie</t>
   </si>
   <si>
     <t>174036004</t>
   </si>
   <si>
-    <t>Emergency appendectomy</t>
+    <t>appendicectomie en urgence</t>
   </si>
   <si>
     <t>174396007</t>
   </si>
   <si>
-    <t>Pilonidal sinus operation</t>
+    <t>opération du sinus pilonidal</t>
   </si>
   <si>
     <t>174776001</t>
   </si>
   <si>
-    <t>Total splenectomy</t>
+    <t>splénectomie totale</t>
   </si>
   <si>
     <t>174822005</t>
   </si>
   <si>
-    <t>Atrial inversion operation using atrial wall</t>
+    <t>inversion auriculaire utilisant la paroi auriculaire</t>
   </si>
   <si>
     <t>174826008</t>
   </si>
   <si>
-    <t>Arterial switch operation</t>
+    <t>intervention chirurgicale de switch artériel</t>
   </si>
   <si>
     <t>174830006</t>
   </si>
   <si>
-    <t>Repair of total anomalous pulmonary venous connection</t>
+    <t>réparation chirurgicale d'un retour veineux pulmonaire total anormal</t>
   </si>
   <si>
     <t>174836000</t>
   </si>
   <si>
-    <t>Repair of defect of the atrioventricular septum</t>
+    <t>fermeture d'une communication auriculoventriculaire</t>
   </si>
   <si>
     <t>174900004</t>
   </si>
   <si>
-    <t>Repair of partial anomalous pulmonary venous connection</t>
+    <t>réparation chirurgicale d'un retour veineux pulmonaire partiel anormal</t>
   </si>
   <si>
     <t>174929002</t>
   </si>
   <si>
-    <t>Mechanical prosthetic aortic valve replacement</t>
+    <t>remplacement de la valve aortique prothétique mécanique</t>
   </si>
   <si>
     <t>175095005</t>
   </si>
   <si>
-    <t>Open ablation of atrioventricular node</t>
+    <t>ablation ouverte du nœud auriculoventriculaire</t>
   </si>
   <si>
     <t>175125003</t>
   </si>
   <si>
-    <t>Percutaneous transluminal ablation of atrioventricular node</t>
+    <t>ablation transluminale percutanée du nœud auriculoventriculaire</t>
   </si>
   <si>
     <t>175135009</t>
   </si>
   <si>
-    <t>Introduction of cardiac pacemaker system via vein</t>
+    <t>introduction d'un système de stimulateur cardiaque par voie veineuse</t>
   </si>
   <si>
     <t>175905003</t>
   </si>
   <si>
-    <t>Total nephrectomy</t>
+    <t>néphrectomie totale</t>
   </si>
   <si>
     <t>176548009</t>
   </si>
   <si>
-    <t>Standard circumcision</t>
+    <t>circoncision ordinaire</t>
   </si>
   <si>
     <t>176766002</t>
   </si>
   <si>
-    <t>Avulsion of lesion of cervix uteri</t>
+    <t>destruction d'une lésion du col de l'utérus</t>
   </si>
   <si>
     <t>176785004</t>
   </si>
   <si>
-    <t>Non-obstetric encircling suture of cervical os</t>
+    <t>cerclage cervical non-obstétrical</t>
   </si>
   <si>
     <t>176795006</t>
   </si>
   <si>
-    <t>Subtotal abdominal hysterectomy</t>
+    <t>hystérectomie subtotale par voie abdominale</t>
   </si>
   <si>
     <t>177141003</t>
   </si>
   <si>
-    <t>Elective cesarean section</t>
+    <t>césarienne élective</t>
   </si>
   <si>
     <t>177142005</t>
   </si>
   <si>
-    <t>Elective upper segment cesarean section</t>
+    <t>césarienne programmée du segment supérieur</t>
   </si>
   <si>
     <t>177143000</t>
   </si>
   <si>
-    <t>Elective lower segment cesarean section</t>
+    <t>césarienne élective du segment inférieur</t>
   </si>
   <si>
     <t>177217006</t>
   </si>
   <si>
-    <t>Immediate repair of obstetric laceration</t>
+    <t>réparation immédiate de déchirure obstétricale</t>
   </si>
   <si>
     <t>177218001</t>
@@ -771,145 +771,145 @@
     <t>177219009</t>
   </si>
   <si>
-    <t>Immediate repair of obstetric laceration of perineum and sphincter of anus</t>
+    <t>réparation immédiate de déchirure obstétricale du périnée et du sphincter de l'anus</t>
   </si>
   <si>
     <t>177220003</t>
   </si>
   <si>
-    <t>Immediate repair of obstetric laceration of vagina and floor of pelvis</t>
+    <t>réparation immédiate de déchirure obstétricale du vagin et du plancher pelvien</t>
   </si>
   <si>
     <t>177221004</t>
   </si>
   <si>
-    <t>Immediate repair of minor obstetric laceration</t>
+    <t>réparation immédiate de déchirure obstétricale mineure</t>
   </si>
   <si>
     <t>177250006</t>
   </si>
   <si>
-    <t>Abdominoplasty</t>
+    <t>abdominoplastie</t>
   </si>
   <si>
     <t>17744000</t>
   </si>
   <si>
-    <t>Subtotal hysterectomy after cesarean delivery</t>
+    <t>hystérectomie subtotale après un accouchement par césarienne</t>
   </si>
   <si>
     <t>177694006</t>
   </si>
   <si>
-    <t>Incision and drainage of wound</t>
+    <t>incision et drainage de plaie</t>
   </si>
   <si>
     <t>177735003</t>
   </si>
   <si>
-    <t>Excision of wedge of nail</t>
+    <t>résection d'un ongle incarné</t>
   </si>
   <si>
     <t>177765008</t>
   </si>
   <si>
-    <t>Opening of chest</t>
+    <t>thoracotomie</t>
   </si>
   <si>
     <t>177854007</t>
   </si>
   <si>
-    <t>Simple excision of inguinal hernial sac</t>
+    <t>excision simple d'un sac herniaire inguinal</t>
   </si>
   <si>
     <t>177860007</t>
   </si>
   <si>
-    <t>Primary repair of inguinal hernia</t>
+    <t>réparation primaire de la hernie inguinale</t>
   </si>
   <si>
     <t>177866001</t>
   </si>
   <si>
-    <t>Bilateral inguinal hernia repair</t>
+    <t>cure bilatérale de hernie inguinale</t>
   </si>
   <si>
     <t>178095009</t>
   </si>
   <si>
-    <t>Excision of ganglion of wrist</t>
+    <t>excision ganglionnaire du poignet</t>
   </si>
   <si>
     <t>178097001</t>
   </si>
   <si>
-    <t>Excision of ganglion of knee</t>
+    <t>excision ganglionnaire du genou</t>
   </si>
   <si>
     <t>178155009</t>
   </si>
   <si>
-    <t>Plastic repair of tendon</t>
+    <t>chirurgie plastique d'un tendon</t>
   </si>
   <si>
     <t>178283002</t>
   </si>
   <si>
-    <t>Block dissection of cervical lymph nodes</t>
+    <t>évidement ganglionnaire cervical en bloc</t>
   </si>
   <si>
     <t>178517008</t>
   </si>
   <si>
-    <t>Primary excision of cervical intervertebral disc</t>
+    <t>excision primaire du disque intervertébral cervical</t>
   </si>
   <si>
     <t>17860005</t>
   </si>
   <si>
-    <t>Low forceps delivery with episiotomy</t>
+    <t>accouchement avec forceps bas avec épisiotomie</t>
   </si>
   <si>
     <t>178618008</t>
   </si>
   <si>
-    <t>Primary lumbar discectomy</t>
+    <t>discectomie lombaire primaire</t>
   </si>
   <si>
     <t>178668000</t>
   </si>
   <si>
-    <t>Percutaneous discectomy</t>
+    <t>discectomie percutanée</t>
   </si>
   <si>
     <t>178814008</t>
   </si>
   <si>
-    <t>Spinal facet joint denervation</t>
+    <t>dénervation des facettes articulaires vertébrales</t>
   </si>
   <si>
     <t>179342005</t>
   </si>
   <si>
-    <t>Knee joint operation</t>
+    <t>intervention chirurgicale de l'articulation d'un genou</t>
   </si>
   <si>
     <t>179381005</t>
   </si>
   <si>
-    <t>Arthroscopic partial medial meniscectomy</t>
+    <t>méniscectomie médiale partielle arthroscopique</t>
   </si>
   <si>
     <t>179382003</t>
   </si>
   <si>
-    <t>Arthroscopic total medial meniscectomy</t>
+    <t>méniscectomie médiale totale arthroscopique</t>
   </si>
   <si>
     <t>179383008</t>
   </si>
   <si>
-    <t>Arthroscopic partial lateral meniscectomy</t>
+    <t>méniscectomie latérale partielle arthroscopique</t>
   </si>
   <si>
     <t>179390003</t>
@@ -921,421 +921,421 @@
     <t>18027006</t>
   </si>
   <si>
-    <t>Transplantation of liver</t>
+    <t>greffe de foie</t>
   </si>
   <si>
     <t>18286008</t>
   </si>
   <si>
-    <t>Catheter ablation of tissue of heart</t>
+    <t>ablation par cathéther de tissu cardiaque</t>
   </si>
   <si>
     <t>18302006</t>
   </si>
   <si>
-    <t>Hysterotomy and termination of pregnancy</t>
+    <t>avortement thérapeutique par hystérotomie</t>
   </si>
   <si>
     <t>183668008</t>
   </si>
   <si>
-    <t>Total avulsion of nail plate</t>
+    <t>avulsion totale de la lame unguéale</t>
   </si>
   <si>
     <t>18557009</t>
   </si>
   <si>
-    <t>Closure by suture</t>
+    <t>fermeture par suture</t>
   </si>
   <si>
     <t>18692006</t>
   </si>
   <si>
-    <t>Bypass gastroenterostomy</t>
+    <t>court-circuit gastrique par gastroentérostomie</t>
   </si>
   <si>
     <t>19063003</t>
   </si>
   <si>
-    <t>Arthroplasty of knee</t>
+    <t>arthroplastie d'un genou</t>
   </si>
   <si>
     <t>19273005</t>
   </si>
   <si>
-    <t>Repair of recurrent inguinal hernia</t>
+    <t>réparation d'une hernie inguinale récidivante</t>
   </si>
   <si>
     <t>195565004</t>
   </si>
   <si>
-    <t>Dilation of esophagus</t>
+    <t>dilatation de l'œsophage</t>
   </si>
   <si>
     <t>19578002</t>
   </si>
   <si>
-    <t>Arthrodesis</t>
+    <t>arthrodèse</t>
   </si>
   <si>
     <t>20418004</t>
   </si>
   <si>
-    <t>Wedge resection</t>
+    <t>résection cunéiforme</t>
   </si>
   <si>
     <t>20701002</t>
   </si>
   <si>
-    <t>Open reduction of fracture with internal fixation</t>
+    <t>réduction ouverte avec fixation interne d'une fracture</t>
   </si>
   <si>
     <t>20805001</t>
   </si>
   <si>
-    <t>Rhinoseptoplasty</t>
+    <t>rhinoseptoplastie</t>
   </si>
   <si>
     <t>21371007</t>
   </si>
   <si>
-    <t>Operation on abdominal region</t>
+    <t>intervention chirurgicale abdominale</t>
   </si>
   <si>
     <t>21574003</t>
   </si>
   <si>
-    <t>Repair of aneurysm of abdominal aorta with graft</t>
+    <t>traitement d'un anévrisme de l'aorte abdominale avec greffe</t>
   </si>
   <si>
     <t>22523008</t>
   </si>
   <si>
-    <t>Vasectomy</t>
+    <t>vasectomie</t>
   </si>
   <si>
     <t>22890008</t>
   </si>
   <si>
-    <t>Augmentation mammoplasty</t>
+    <t>mammoplastie d'augmentation</t>
   </si>
   <si>
     <t>230810008</t>
   </si>
   <si>
-    <t>Excision of tumor of brain meninges</t>
+    <t>ablation d'un néoplasme méningé</t>
   </si>
   <si>
     <t>231751005</t>
   </si>
   <si>
-    <t>Exchange of intraocular lens</t>
+    <t>remplacement d'une lentille intraoculaire</t>
   </si>
   <si>
     <t>232470004</t>
   </si>
   <si>
-    <t>Reconstruction of nose</t>
+    <t>reconstruction du nez</t>
   </si>
   <si>
     <t>232632009</t>
   </si>
   <si>
-    <t>Wedge excision of lung</t>
+    <t>résection cunéiforme du poumon</t>
   </si>
   <si>
     <t>232658009</t>
   </si>
   <si>
-    <t>Double lung transplant</t>
+    <t>transplantation bipulmonaire</t>
   </si>
   <si>
     <t>232717009</t>
   </si>
   <si>
-    <t>Coronary artery bypass graft</t>
+    <t>pontage coronarien</t>
   </si>
   <si>
     <t>232720001</t>
   </si>
   <si>
-    <t>Coronary artery bypass grafts x 2</t>
+    <t>double pontage coronaire</t>
   </si>
   <si>
     <t>232721002</t>
   </si>
   <si>
-    <t>Coronary artery bypass grafts x 3</t>
+    <t>pontage aorto-coronaire triple</t>
   </si>
   <si>
     <t>232722009</t>
   </si>
   <si>
-    <t>Coronary artery bypass grafts x 4</t>
+    <t>quadruple pontage coronarien</t>
   </si>
   <si>
     <t>232723004</t>
   </si>
   <si>
-    <t>Coronary artery bypass grafts x 5</t>
+    <t>quintuple pontage coronarien</t>
   </si>
   <si>
     <t>232841002</t>
   </si>
   <si>
-    <t>Repair of implanted aortic paravalvular leak</t>
+    <t>réparation d'une fuite paravalvulaire de la prothèse de valve aortique</t>
   </si>
   <si>
     <t>233022006</t>
   </si>
   <si>
-    <t>Construction of conduit - right atrium to pulmonary trunk</t>
+    <t>pontage de l'oreillette droite au tronc pulmonaire</t>
   </si>
   <si>
     <t>233134001</t>
   </si>
   <si>
-    <t>Damus-Stansel-Kaye operation</t>
+    <t>intervention de Damus-Kaye-Stansel</t>
   </si>
   <si>
     <t>233139006</t>
   </si>
   <si>
-    <t>Norwood type operation</t>
+    <t>intervention de Norwood</t>
   </si>
   <si>
     <t>233159005</t>
   </si>
   <si>
-    <t>Ablation operation for arrhythmia</t>
+    <t>ablation pour arythmie</t>
   </si>
   <si>
     <t>233161001</t>
   </si>
   <si>
-    <t>Cryoablation operation for arrhythmia</t>
+    <t>cryoablation pour arythmie</t>
   </si>
   <si>
     <t>233163003</t>
   </si>
   <si>
-    <t>Radiofrequency ablation operation for arrhythmia</t>
+    <t>ablation par radiofréquence pour arythmie</t>
   </si>
   <si>
     <t>233170003</t>
   </si>
   <si>
-    <t>Implantation of automatic cardiac defibrillator</t>
+    <t>implantation d'un défibrillateur cardiaque automatique</t>
   </si>
   <si>
     <t>233171004</t>
   </si>
   <si>
-    <t>Removal of automatic cardiac defibrillator</t>
+    <t>retrait d'un défibrillateur cardiaque automatique</t>
   </si>
   <si>
     <t>233188006</t>
   </si>
   <si>
-    <t>Removal of cardiac pacing electrode</t>
+    <t>retrait d'une électrode de stimulateur cardiaque</t>
   </si>
   <si>
     <t>233199008</t>
   </si>
   <si>
-    <t>Closure of ductus arteriosus with clip</t>
+    <t>fermeture du canal artériel par clip</t>
   </si>
   <si>
     <t>233224003</t>
   </si>
   <si>
-    <t>Central aortopulmonary shunt operation</t>
+    <t>intervention avec shunt aortopulmonaire central</t>
   </si>
   <si>
     <t>233230003</t>
   </si>
   <si>
-    <t>Hemi-Fontan operation</t>
+    <t>intervention de hémi-Fontan</t>
   </si>
   <si>
     <t>233370007</t>
   </si>
   <si>
-    <t>Aortic aneurysm repair</t>
+    <t>réparation de l'anévrisme de l'aorte</t>
   </si>
   <si>
     <t>233445008</t>
   </si>
   <si>
-    <t>Transjugular intrahepatic portosystemic shunt</t>
+    <t>shunt intrahépatique portosystémique transjugulaire</t>
   </si>
   <si>
     <t>233456008</t>
   </si>
   <si>
-    <t>Stripping of vein</t>
+    <t>éveinage</t>
   </si>
   <si>
     <t>234319005</t>
   </si>
   <si>
-    <t>Splenectomy</t>
+    <t>splénectomie</t>
   </si>
   <si>
     <t>234336002</t>
   </si>
   <si>
-    <t>Hemopoietic stem cell transplant</t>
+    <t>transplantation de cellules souches hématopoïétiques</t>
   </si>
   <si>
     <t>234647001</t>
   </si>
   <si>
-    <t>Repair of cleft lip</t>
+    <t>réparation d'une fente labiale</t>
   </si>
   <si>
     <t>234650003</t>
   </si>
   <si>
-    <t>Repair of bilateral cleft lip</t>
+    <t>réparation d'une fente labiale bilatérale</t>
   </si>
   <si>
     <t>234890003</t>
   </si>
   <si>
-    <t>Repair of cleft palate</t>
+    <t>réparation d'une fente palatine</t>
   </si>
   <si>
     <t>234891004</t>
   </si>
   <si>
-    <t>Repair of cleft of hard palate</t>
+    <t>réparation chirurgicale d'une fente du palais dur</t>
   </si>
   <si>
     <t>234892006</t>
   </si>
   <si>
-    <t>Repair of cleft of soft palate</t>
+    <t>réparation d'une fente du palais mou</t>
   </si>
   <si>
     <t>235159007</t>
   </si>
   <si>
-    <t>Percutaneous endoscopic gastrostomy</t>
+    <t>gastrostomie endoscopique percutanée</t>
   </si>
   <si>
     <t>235570008</t>
   </si>
   <si>
-    <t>Dilatation of bile duct</t>
+    <t>dilatation biliaire</t>
   </si>
   <si>
     <t>236886002</t>
   </si>
   <si>
-    <t>Hysterectomy</t>
+    <t>hystérectomie</t>
   </si>
   <si>
     <t>236887006</t>
   </si>
   <si>
-    <t>Laparoscopic hysterectomy</t>
+    <t>hystérectomie laparoscopique</t>
   </si>
   <si>
     <t>236946009</t>
   </si>
   <si>
-    <t>Macdonald's cervical cerclage</t>
+    <t>cerclage cervical par la technique de Mac Donald</t>
   </si>
   <si>
     <t>236947000</t>
   </si>
   <si>
-    <t>Shirodkar's cervical cerclage</t>
+    <t>cerclage cervical par la technique de Shirodkar</t>
   </si>
   <si>
     <t>236985002</t>
   </si>
   <si>
-    <t>Emergency lower segment cesarean section</t>
+    <t>césarienne en urgence avec incision du segment inférieur de l'utérus</t>
   </si>
   <si>
     <t>236986001</t>
   </si>
   <si>
-    <t>Emergency upper segment cesarean section</t>
+    <t>césarienne en urgence avec incision du segment supérieur de l'utérus</t>
   </si>
   <si>
     <t>236987005</t>
   </si>
   <si>
-    <t>Emergency cesarean hysterectomy</t>
+    <t>césarienne en urgence avec hystérectomie</t>
   </si>
   <si>
     <t>236988000</t>
   </si>
   <si>
-    <t>Elective cesarean hysterectomy</t>
+    <t>césarienne et hystérectomie programmées</t>
   </si>
   <si>
     <t>236989008</t>
   </si>
   <si>
-    <t>Abdominal delivery for shoulder dystocia</t>
+    <t>césarienne pour une dystocie des épaules</t>
   </si>
   <si>
     <t>236991000</t>
   </si>
   <si>
-    <t>Operation to facilitate delivery</t>
+    <t>intervention chirurgicale pour faciliter l'accouchement</t>
   </si>
   <si>
     <t>237406004</t>
   </si>
   <si>
-    <t>Plastic operation on the breast</t>
+    <t>chirurgie plastique du sein</t>
   </si>
   <si>
     <t>238192002</t>
   </si>
   <si>
-    <t>Repair of ventral hernia</t>
+    <t>cure d'une hernie de la paroi abdominale antérieure</t>
   </si>
   <si>
     <t>239431009</t>
   </si>
   <si>
-    <t>Reconstruction of anterior cruciate ligament of knee joint</t>
+    <t>reconstruction du ligament croisé antérieur de l'articulation du genou</t>
   </si>
   <si>
     <t>239503002</t>
   </si>
   <si>
-    <t>Resurfacing of the patella</t>
+    <t>resurfaçage de la patella</t>
   </si>
   <si>
     <t>23968004</t>
   </si>
   <si>
-    <t>Excision of colon</t>
+    <t>colectomie</t>
   </si>
   <si>
     <t>243306000</t>
   </si>
   <si>
-    <t>Ureteroileostomy</t>
+    <t>urétéro-iléostomie</t>
   </si>
   <si>
     <t>24443003</t>
   </si>
   <si>
-    <t>Total thyroidectomy</t>
+    <t>thyroïdectomie totale</t>
   </si>
   <si>
     <t>24496007</t>
   </si>
   <si>
-    <t>Hemorrhoidectomy</t>
+    <t>hémorroïdectomie</t>
   </si>
   <si>
     <t>245544005</t>
@@ -1347,49 +1347,49 @@
     <t>248273008</t>
   </si>
   <si>
-    <t>Aspiration curettage of uterus after delivery</t>
+    <t>curetage de l'utérus par aspiration après accouchement</t>
   </si>
   <si>
     <t>250980009</t>
   </si>
   <si>
-    <t>Cardioversion</t>
+    <t>cardioversion</t>
   </si>
   <si>
     <t>25353009</t>
   </si>
   <si>
-    <t>Craniotomy</t>
+    <t>craniotomie</t>
   </si>
   <si>
     <t>257822003</t>
   </si>
   <si>
-    <t>Extracapsular extraction</t>
+    <t>extraction extracapsulaire</t>
   </si>
   <si>
     <t>257833000</t>
   </si>
   <si>
-    <t>Internal fixation using staple</t>
+    <t>fixation interne avec agrafe</t>
   </si>
   <si>
     <t>257834006</t>
   </si>
   <si>
-    <t>Internal fixation using screw</t>
+    <t>fixation interne avec vis</t>
   </si>
   <si>
     <t>257835007</t>
   </si>
   <si>
-    <t>Internal fixation using plate</t>
+    <t>fixation interne avec plaque</t>
   </si>
   <si>
     <t>25828002</t>
   </si>
   <si>
-    <t>Mid forceps delivery with episiotomy</t>
+    <t>accouchement avec forceps moyen avec épisiotomie</t>
   </si>
   <si>
     <t>260216002</t>
@@ -1401,169 +1401,169 @@
     <t>26212005</t>
   </si>
   <si>
-    <t>Replacement of aortic valve</t>
+    <t>remplacement de la valve aortique</t>
   </si>
   <si>
     <t>26294005</t>
   </si>
   <si>
-    <t>Radical prostatectomy</t>
+    <t>prostatectomie radicale</t>
   </si>
   <si>
     <t>26313002</t>
   </si>
   <si>
-    <t>Delivery by vacuum extraction with episiotomy</t>
+    <t>accouchement par extraction par ventouse avec épisiotomie</t>
   </si>
   <si>
     <t>26390003</t>
   </si>
   <si>
-    <t>Total colectomy</t>
+    <t>exérèse du côlon</t>
   </si>
   <si>
     <t>26476002</t>
   </si>
   <si>
-    <t>Operation on bronchus</t>
+    <t>intervention chirurgicale des bronches</t>
   </si>
   <si>
     <t>264959005</t>
   </si>
   <si>
-    <t>Primary repair of femoral hernia</t>
+    <t>réparation primaire de la hernie fémorale</t>
   </si>
   <si>
     <t>265056007</t>
   </si>
   <si>
-    <t>Vaginal hysterectomy</t>
+    <t>hystérectomie vaginale</t>
   </si>
   <si>
     <t>265060005</t>
   </si>
   <si>
-    <t>Endometrial ablation</t>
+    <t>ablation de l'endomètre</t>
   </si>
   <si>
     <t>265132005</t>
   </si>
   <si>
-    <t>Primary open reduction and internal fixation of proximal femoral fracture with screw/nail and plate device</t>
+    <t>réduction ouverte primaire et fixation interne d'une fracture fémorale proximale avec un dispositif de vis/clous et plaque</t>
   </si>
   <si>
     <t>265157000</t>
   </si>
   <si>
-    <t>Total prosthetic replacement of hip joint using cement</t>
+    <t>implantation d'une prothèse totale de hanche cimentée</t>
   </si>
   <si>
     <t>265170009</t>
   </si>
   <si>
-    <t>Total prosthetic replacement of knee joint using cement</t>
+    <t>arthroplastie de l'articulation d'un genou par prothèse totale cimentée</t>
   </si>
   <si>
     <t>265250008</t>
   </si>
   <si>
-    <t>Reduction mammoplasty, bilateral</t>
+    <t>mammoplastie de réduction bilatérale</t>
   </si>
   <si>
     <t>265472007</t>
   </si>
   <si>
-    <t>Plastic repair of mitral valve</t>
+    <t>valvuloplastie mitrale</t>
   </si>
   <si>
     <t>265473002</t>
   </si>
   <si>
-    <t>Plastic repair of aortic valve</t>
+    <t>plastie de la valve aortique</t>
   </si>
   <si>
     <t>265542003</t>
   </si>
   <si>
-    <t>Ligation of long saphenous vein</t>
+    <t>ligature de la veine grande saphène</t>
   </si>
   <si>
     <t>265636007</t>
   </si>
   <si>
-    <t>Cerclage of uterine cervix</t>
+    <t>cerclage du col utérin</t>
   </si>
   <si>
     <t>265703000</t>
   </si>
   <si>
-    <t>Jaw and temporomandibular joint operations</t>
+    <t>intervention chirurgicale de la mâchoire et des articulations temporomandibulaires</t>
   </si>
   <si>
     <t>26578004</t>
   </si>
   <si>
-    <t>Hysterotomy with removal of hydatidiform mole</t>
+    <t>hystérotomie avec résection de môle hydatiforme</t>
   </si>
   <si>
     <t>265855005</t>
   </si>
   <si>
-    <t>Varicose vein stripping</t>
+    <t>éveinage des varices</t>
   </si>
   <si>
     <t>26786002</t>
   </si>
   <si>
-    <t>Scleral buckling</t>
+    <t>indentation sclérale</t>
   </si>
   <si>
     <t>27315000</t>
   </si>
   <si>
-    <t>Removal of breast implant</t>
+    <t>retrait d'un implant mammaire</t>
   </si>
   <si>
     <t>274022008</t>
   </si>
   <si>
-    <t>Repair of coarctation of aorta</t>
+    <t>réparation chirurgicale d'une coarctation de l'aorte</t>
   </si>
   <si>
     <t>274023003</t>
   </si>
   <si>
-    <t>Varicose vein operation</t>
+    <t>opération de varices</t>
   </si>
   <si>
     <t>274068006</t>
   </si>
   <si>
-    <t>Excision of lipoma</t>
+    <t>excision d'un lipome</t>
   </si>
   <si>
     <t>274330002</t>
   </si>
   <si>
-    <t>Surgical biopsy</t>
+    <t>biopsie chirurgicale</t>
   </si>
   <si>
     <t>274331003</t>
   </si>
   <si>
-    <t>Surgical biopsy of breast</t>
+    <t>biopsie chirurgicale du sein</t>
   </si>
   <si>
     <t>27480002</t>
   </si>
   <si>
-    <t>Excision of bunion</t>
+    <t>excision d'oignon</t>
   </si>
   <si>
     <t>275001008</t>
   </si>
   <si>
-    <t>Myringotomy and insertion of long-term ventilation tube</t>
+    <t>myringotomie et mise en place d'un aérateur transtympanique longue durée</t>
   </si>
   <si>
     <t>275035006</t>
@@ -1575,193 +1575,193 @@
     <t>275227003</t>
   </si>
   <si>
-    <t>Myocardial revascularization</t>
+    <t>revascularisation myocardique</t>
   </si>
   <si>
     <t>277764006</t>
   </si>
   <si>
-    <t>Fusion of posterior lumbar spine</t>
+    <t>arthrodèse lombaire postérieure</t>
   </si>
   <si>
     <t>282191000</t>
   </si>
   <si>
-    <t>Laminotomy for decompression and exploration</t>
+    <t>laminectomie pour la décompression et l'exploration</t>
   </si>
   <si>
     <t>284181007</t>
   </si>
   <si>
-    <t>Incision and drainage of abscess</t>
+    <t>incision et drainage d'un abcès</t>
   </si>
   <si>
     <t>284532000</t>
   </si>
   <si>
-    <t>Myringotomy and insertion of tympanic ventilation tube</t>
+    <t>myringotomie et mise en place d'un aérateur transtympanique</t>
   </si>
   <si>
     <t>285662005</t>
   </si>
   <si>
-    <t>Removal of plate from bone</t>
+    <t>retrait d'une plaque d'ostéosynthèse</t>
   </si>
   <si>
     <t>285663000</t>
   </si>
   <si>
-    <t>Removal of bone screw from bone</t>
+    <t>enlèvement des vis osseuses</t>
   </si>
   <si>
     <t>287310004</t>
   </si>
   <si>
-    <t>Lung tumor excision</t>
+    <t>excision d'un néoplasme du poumon</t>
   </si>
   <si>
     <t>287664005</t>
   </si>
   <si>
-    <t>Bilateral tubal ligation</t>
+    <t>ligature tubaire bilatérale</t>
   </si>
   <si>
     <t>28768007</t>
   </si>
   <si>
-    <t>Incisional biopsy of breast mass</t>
+    <t>biopsie incisionnelle d'une masse du sein</t>
   </si>
   <si>
     <t>287977004</t>
   </si>
   <si>
-    <t>Dilation/incision of cervix - delivery aid</t>
+    <t>dilatation ou incision du col de l'utérus, aide à l'accouchement</t>
   </si>
   <si>
     <t>288042004</t>
   </si>
   <si>
-    <t>Hysterectomy and fetus removal</t>
+    <t>hystérectomie et extraction du fœtus</t>
   </si>
   <si>
     <t>288043009</t>
   </si>
   <si>
-    <t>Hysterectomy in pregnancy</t>
+    <t>hystérectomie pendant la grossesse</t>
   </si>
   <si>
     <t>28913000</t>
   </si>
   <si>
-    <t>Tonsillectomy and adenoidectomy</t>
+    <t>amygdalectomie et adénoïdectomie</t>
   </si>
   <si>
     <t>297709009</t>
   </si>
   <si>
-    <t>Open acromioplasty for decompression of rotator cuff</t>
+    <t>acromioplastie ouverte pour la décompression de la coiffe des rotateurs</t>
   </si>
   <si>
     <t>29827000</t>
   </si>
   <si>
-    <t>Bilateral salpingectomy with oophorectomy</t>
+    <t>excision bilatérale des salpinx et des ovaires</t>
   </si>
   <si>
     <t>300009002</t>
   </si>
   <si>
-    <t>Removal of acoustic neuroma</t>
+    <t>ablation d'un neurinome de l'acoustique</t>
   </si>
   <si>
     <t>300589005</t>
   </si>
   <si>
-    <t>Excision of sebaceous cyst</t>
+    <t>excision d'un kyste sébacé</t>
   </si>
   <si>
     <t>30123000</t>
   </si>
   <si>
-    <t>Repair of atrial septal defect with prosthesis by closed heart technique</t>
+    <t>fermeture par chirurgie à cœur fermé d'une communication interatriale avec prothèse</t>
   </si>
   <si>
     <t>301889008</t>
   </si>
   <si>
-    <t>Excision of malignant skin tumor</t>
+    <t>excision d'une tumeur maligne de la peau</t>
   </si>
   <si>
     <t>301890004</t>
   </si>
   <si>
-    <t>Excision of skin cyst</t>
+    <t>excision d'un kyste de la peau</t>
   </si>
   <si>
     <t>302190000</t>
   </si>
   <si>
-    <t>Abdominal hysterectomy and right salpingo-oophorectomy</t>
+    <t>hystérectomie abdominale et salpingo-ovariectomie droite</t>
   </si>
   <si>
     <t>302191001</t>
   </si>
   <si>
-    <t>Abdominal hysterectomy and left salpingo-oophorectomy</t>
+    <t>hystérectomie abdominale et salpingo-ovariectomie gauche</t>
   </si>
   <si>
     <t>302343007</t>
   </si>
   <si>
-    <t>Insertion of prosthesis for breast</t>
+    <t>insertion d'une prothèse mammaire</t>
   </si>
   <si>
     <t>302369001</t>
   </si>
   <si>
-    <t>Clitoridectomy</t>
+    <t>clitoridectomie</t>
   </si>
   <si>
     <t>302441008</t>
   </si>
   <si>
-    <t>Liposuction of subcutaneous tissue</t>
+    <t>lipoaspiration du tissu sous-cutané</t>
   </si>
   <si>
     <t>302490008</t>
   </si>
   <si>
-    <t>Arthroscopic meniscectomy</t>
+    <t>méniscectomie arthroscopique</t>
   </si>
   <si>
     <t>302605004</t>
   </si>
   <si>
-    <t>Forced manual dilatation of anus</t>
+    <t>dilatation manuelle forcée de l'anus</t>
   </si>
   <si>
     <t>303633008</t>
   </si>
   <si>
-    <t>Irrigation of maxillary antrum</t>
+    <t>irrigation de l'antre de Highmore</t>
   </si>
   <si>
     <t>303648002</t>
   </si>
   <si>
-    <t>Excision of papilloma</t>
+    <t>excision d'un papillome</t>
   </si>
   <si>
     <t>303650005</t>
   </si>
   <si>
-    <t>Removal of mole of skin by excision</t>
+    <t>ablation d'un grain de beauté de la peau par excision</t>
   </si>
   <si>
     <t>304040003</t>
   </si>
   <si>
-    <t>Grafting to skin</t>
+    <t>greffe cutanée</t>
   </si>
   <si>
     <t>30542005</t>
@@ -1773,7 +1773,7 @@
     <t>307273008</t>
   </si>
   <si>
-    <t>Cautery of wart</t>
+    <t>cautérisation d'une verrue</t>
   </si>
   <si>
     <t>307279007</t>
@@ -1785,73 +1785,73 @@
     <t>307280005</t>
   </si>
   <si>
-    <t>Implantation of cardiac pacemaker</t>
+    <t>implantation d'un stimulateur cardiaque</t>
   </si>
   <si>
     <t>307771009</t>
   </si>
   <si>
-    <t>Radical abdominal hysterectomy</t>
+    <t>hystérectomie abdominale radicale</t>
   </si>
   <si>
     <t>308665009</t>
   </si>
   <si>
-    <t>Repair of pulmonary valve with tissue graft</t>
+    <t>réparation de valve pulmonaire par greffe tissulaire</t>
   </si>
   <si>
     <t>308695001</t>
   </si>
   <si>
-    <t>Intracapsular cataract extraction and insertion of intraocular lens</t>
+    <t>extraction intracapsulaire de la cataracte et insertion de lentille intraoculaire</t>
   </si>
   <si>
     <t>308696000</t>
   </si>
   <si>
-    <t>Coarctation angioplasty</t>
+    <t>angioplastie de coarctation</t>
   </si>
   <si>
     <t>30880003</t>
   </si>
   <si>
-    <t>Trabeculectomy ab externo</t>
+    <t>trabéculectomie externe</t>
   </si>
   <si>
     <t>30904006</t>
   </si>
   <si>
-    <t>Vascular surgery procedure</t>
+    <t>intervention chirurgicale vasculaire</t>
   </si>
   <si>
     <t>309430005</t>
   </si>
   <si>
-    <t>Excision of skin tag</t>
+    <t>exérèse d'acrochordon</t>
   </si>
   <si>
     <t>30956003</t>
   </si>
   <si>
-    <t>Subtotal thyroidectomy</t>
+    <t>thyroïdectomie subtotale</t>
   </si>
   <si>
     <t>309879006</t>
   </si>
   <si>
-    <t>Abdominal hysterocolpectomy</t>
+    <t>colpohystérectomie par voie abdominale</t>
   </si>
   <si>
     <t>310582005</t>
   </si>
   <si>
-    <t>Implantation of intravenous dual chamber permanent pacemaker</t>
+    <t>pose de stimulateur cardiaque permanent double chambre par voie intraveineuse</t>
   </si>
   <si>
     <t>311774002</t>
   </si>
   <si>
-    <t>Colonoscopic polypectomy</t>
+    <t>polypectomie par colonoscopie</t>
   </si>
   <si>
     <t>312235007</t>
@@ -1863,43 +1863,43 @@
     <t>312775003</t>
   </si>
   <si>
-    <t>Debridement of ulcer</t>
+    <t>débridement d'un ulcère</t>
   </si>
   <si>
     <t>312965008</t>
   </si>
   <si>
-    <t>Laser assisted in situ keratomileusis</t>
+    <t>kératomileusis in situ au laser</t>
   </si>
   <si>
     <t>312968005</t>
   </si>
   <si>
-    <t>Excision biopsy of skin lesion</t>
+    <t>biopsie d'excision de la lésion cutanée</t>
   </si>
   <si>
     <t>313039003</t>
   </si>
   <si>
-    <t>Solid organ transplant (procedure)</t>
+    <t>greffe d'un organe plein</t>
   </si>
   <si>
     <t>313270001</t>
   </si>
   <si>
-    <t>Percutaneous insertion of nephrostomy tube</t>
+    <t>insertion percutanée d'une sonde de néphrostomie</t>
   </si>
   <si>
     <t>314128006</t>
   </si>
   <si>
-    <t>Laparoscopic Nissen fundoplication using abdominal approach</t>
+    <t>fundoplicature laparoscopique de Nissen par voie abdominal</t>
   </si>
   <si>
     <t>315308008</t>
   </si>
   <si>
-    <t>Dilatation of cervix for delivery</t>
+    <t>dilatation du col utérin pour l'accouchement</t>
   </si>
   <si>
     <t>31932005</t>
@@ -1911,61 +1911,61 @@
     <t>32413006</t>
   </si>
   <si>
-    <t>Transplantation of heart</t>
+    <t>greffe cardiaque</t>
   </si>
   <si>
     <t>32477003</t>
   </si>
   <si>
-    <t>Heart-lung transplant with recipient cardiectomy-pneumonectomy</t>
+    <t>transplantation cœur-poumon avec cardiectomie-pneumonectomie du receveur</t>
   </si>
   <si>
     <t>33149006</t>
   </si>
   <si>
-    <t>Pancreatectomy</t>
+    <t>pancréatectomie</t>
   </si>
   <si>
     <t>33496007</t>
   </si>
   <si>
-    <t>Mammoplasty</t>
+    <t>reconstruction mammaire</t>
   </si>
   <si>
     <t>34068001</t>
   </si>
   <si>
-    <t>Heart valve replacement</t>
+    <t>remplacement d'une valve cardiaque</t>
   </si>
   <si>
     <t>3418002</t>
   </si>
   <si>
-    <t>Discectomy of spine</t>
+    <t>discectomie</t>
   </si>
   <si>
     <t>34969007</t>
   </si>
   <si>
-    <t>Operation on retroperitoneum</t>
+    <t>intervention chirurgicale du rétropéritoine</t>
   </si>
   <si>
     <t>3515001</t>
   </si>
   <si>
-    <t>Replacement of electronic heart device, pulse generator</t>
+    <t>remplacement du générateur d'impulsions d'un dispositif cardiaque électronique</t>
   </si>
   <si>
     <t>35350000</t>
   </si>
   <si>
-    <t>Implantation of aortic valve prosthesis or synthetic device</t>
+    <t>pose de valve aortique prothétique ou synthétique</t>
   </si>
   <si>
     <t>35646002</t>
   </si>
   <si>
-    <t>Excision of lesion of skin</t>
+    <t>excision d'une lésion cutanée</t>
   </si>
   <si>
     <t>35860002</t>
@@ -1977,331 +1977,331 @@
     <t>359551000</t>
   </si>
   <si>
-    <t>Angioplasty of vein</t>
+    <t>angioplastie d'une veine</t>
   </si>
   <si>
     <t>359608009</t>
   </si>
   <si>
-    <t>Implantation of cochlear prosthetic device, electrode and receiver</t>
+    <t>pose d'implant cochléaire, électrode et récepteur</t>
   </si>
   <si>
     <t>359612003</t>
   </si>
   <si>
-    <t>Implantation of cochlear prosthetic device</t>
+    <t>implantation d'un appareil prothétique cochléaire</t>
   </si>
   <si>
     <t>359623004</t>
   </si>
   <si>
-    <t>Total lobectomy of lung</t>
+    <t>lobectomie totale du poumon</t>
   </si>
   <si>
     <t>359901001</t>
   </si>
   <si>
-    <t>Neuroplasty and transposition of median nerve at carpal tunnel</t>
+    <t>neuroplastie et transposition du nerf médian du canal carpien</t>
   </si>
   <si>
     <t>359908007</t>
   </si>
   <si>
-    <t>Repair of paraesophageal diaphragmatic hernia</t>
+    <t>traitement d'hernie diaphragmatique paraoesophagienne</t>
   </si>
   <si>
     <t>361222003</t>
   </si>
   <si>
-    <t>Wertheim-Meigs abdominal hysterectomy</t>
+    <t>hystérectomie abdominale selon Wertheim-Meigs</t>
   </si>
   <si>
     <t>361223008</t>
   </si>
   <si>
-    <t>Wertheim operation</t>
+    <t>colpohystérectomie totale élargie</t>
   </si>
   <si>
     <t>36228007</t>
   </si>
   <si>
-    <t>Ophthalmic examination and evaluation</t>
+    <t>examen et évaluation ophtalmologique</t>
   </si>
   <si>
     <t>363187007</t>
   </si>
   <si>
-    <t>Limb operation</t>
+    <t>intervention chirurgicale sur un membre</t>
   </si>
   <si>
     <t>36969009</t>
   </si>
   <si>
-    <t>Placement of stent in coronary artery</t>
+    <t>pose de stent dans l'artère coronaire</t>
   </si>
   <si>
     <t>370611004</t>
   </si>
   <si>
-    <t>Excision of malignant neoplasm</t>
+    <t>excision d'un néoplasme malin</t>
   </si>
   <si>
     <t>370612006</t>
   </si>
   <si>
-    <t>Excision of neoplasm</t>
+    <t>tumorectomie</t>
   </si>
   <si>
     <t>371186005</t>
   </si>
   <si>
-    <t>Amputation of toe</t>
+    <t>amputation d'un orteil</t>
   </si>
   <si>
     <t>3713005</t>
   </si>
   <si>
-    <t>Release for de Quervain's tenosynovitis of hand</t>
+    <t>libération d'une ténosynovite de Quervain</t>
   </si>
   <si>
     <t>371345007</t>
   </si>
   <si>
-    <t>Laser iridotomy</t>
+    <t>iridotomie au laser</t>
   </si>
   <si>
     <t>37153009</t>
   </si>
   <si>
-    <t>Implantation of heart valve with tissue graft</t>
+    <t>pose d'une valve cardiaque avec greffe tissulaire</t>
   </si>
   <si>
     <t>37236007</t>
   </si>
   <si>
-    <t>Dermabrasion</t>
+    <t>dermabrasion</t>
   </si>
   <si>
     <t>373353005</t>
   </si>
   <si>
-    <t>Surgical procedure on eye proper</t>
+    <t>intervention chirurgicale oculaire</t>
   </si>
   <si>
     <t>373415004</t>
   </si>
   <si>
-    <t>Implantation of posterior chamber intraocular lens</t>
+    <t>implantation d'une lentille intraoculaire dans une chambre postérieure</t>
   </si>
   <si>
     <t>37508003</t>
   </si>
   <si>
-    <t>Operation on neck</t>
+    <t>intervention chirurgicale sur le cou</t>
   </si>
   <si>
     <t>38102005</t>
   </si>
   <si>
-    <t>Cholecystectomy</t>
+    <t>cholécystectomie</t>
   </si>
   <si>
     <t>384641003</t>
   </si>
   <si>
-    <t>Repair of mitral valve</t>
+    <t>réparation de la valve mitrale</t>
   </si>
   <si>
     <t>384642005</t>
   </si>
   <si>
-    <t>Mitral valvuloplasty</t>
+    <t>valvuloplastie de la valve mitrale</t>
   </si>
   <si>
     <t>384643000</t>
   </si>
   <si>
-    <t>Repair of tricuspid valve</t>
+    <t>réparation chirurgicale de la valve tricuspide</t>
   </si>
   <si>
     <t>384692006</t>
   </si>
   <si>
-    <t>Intracavitary brachytherapy</t>
+    <t>brachythérapie endocavitaire</t>
   </si>
   <si>
     <t>384723003</t>
   </si>
   <si>
-    <t>Radical mastectomy</t>
+    <t>mastectomie radicale</t>
   </si>
   <si>
     <t>385468004</t>
   </si>
   <si>
-    <t>Cataract extraction and insertion of intraocular lens</t>
+    <t>extraction d'une cataracte et insertion d'une lentille intraoculaire</t>
   </si>
   <si>
     <t>385487005</t>
   </si>
   <si>
-    <t>Surgical procedure on thorax</t>
+    <t>intervention chirurgicale thoracique</t>
   </si>
   <si>
     <t>385488000</t>
   </si>
   <si>
-    <t>Surgical procedure on chest wall</t>
+    <t>intervention chirurgicale de la cage thoracique</t>
   </si>
   <si>
     <t>386556002</t>
   </si>
   <si>
-    <t>Repair of middle ear</t>
+    <t>réparation d'une oreille moyenne</t>
   </si>
   <si>
     <t>386638009</t>
   </si>
   <si>
-    <t>Obstetric operation</t>
+    <t>chirurgie obstétricale</t>
   </si>
   <si>
     <t>386765006</t>
   </si>
   <si>
-    <t>Operation on mediastinum</t>
+    <t>intervention chirurgicale médiastinale</t>
   </si>
   <si>
     <t>387643005</t>
   </si>
   <si>
-    <t>Partial hysterectomy</t>
+    <t>hystérectomie subtotale</t>
   </si>
   <si>
     <t>387644004</t>
   </si>
   <si>
-    <t>Supracervical hysterectomy</t>
+    <t>hystérectomie supracervicale</t>
   </si>
   <si>
     <t>387711001</t>
   </si>
   <si>
-    <t>Pubiotomy to assist delivery</t>
+    <t>pubiotomie d'aide pour un accouchement</t>
   </si>
   <si>
     <t>387713003</t>
   </si>
   <si>
-    <t>Surgical procedure</t>
+    <t>intervention chirurgicale</t>
   </si>
   <si>
     <t>387714009</t>
   </si>
   <si>
-    <t>Operation on lung</t>
+    <t>intervention chirurgicale sur le poumon</t>
   </si>
   <si>
     <t>387731002</t>
   </si>
   <si>
-    <t>Laminectomy</t>
+    <t>laminectomie</t>
   </si>
   <si>
     <t>387740003</t>
   </si>
   <si>
-    <t>Removal of ovarian cyst</t>
+    <t>ablation d'un kyste ovarien</t>
   </si>
   <si>
     <t>38829003</t>
   </si>
   <si>
-    <t>Partial excision</t>
+    <t>excision partielle</t>
   </si>
   <si>
     <t>391998006</t>
   </si>
   <si>
-    <t>Dilation and curettage of uterus after delivery</t>
+    <t>dilatation et curetage de l'utérus après l'accouchement</t>
   </si>
   <si>
     <t>392000009</t>
   </si>
   <si>
-    <t>Hysterotomy for retained placenta</t>
+    <t>hystérotomie pour rétention placentaire</t>
   </si>
   <si>
     <t>392011001</t>
   </si>
   <si>
-    <t>Operation on skin</t>
+    <t>intervention chirurgicale cutanée</t>
   </si>
   <si>
     <t>39202005</t>
   </si>
   <si>
-    <t>Coronary artery bypass with autogenous graft, four grafts</t>
+    <t>quadruple pontage coronarien par autogreffe</t>
   </si>
   <si>
     <t>392021009</t>
   </si>
   <si>
-    <t>Lumpectomy of breast</t>
+    <t>tumorectomie du sein</t>
   </si>
   <si>
     <t>392048005</t>
   </si>
   <si>
-    <t>Operation on urinary system</t>
+    <t>intervention chirurgicale du système urinaire</t>
   </si>
   <si>
     <t>392090004</t>
   </si>
   <si>
-    <t>Operation on breast</t>
+    <t>intervention chirurgicale du sein</t>
   </si>
   <si>
     <t>392236004</t>
   </si>
   <si>
-    <t>Operative procedure on spinal structure</t>
+    <t>intervention chirurgicale sur la région de la colonne vertébrale</t>
   </si>
   <si>
     <t>395218007</t>
   </si>
   <si>
-    <t>Implantation of internal cardiac defibrillator</t>
+    <t>implantation d'un défibrillateur cardiaque interne</t>
   </si>
   <si>
     <t>396490007</t>
   </si>
   <si>
-    <t>Myringoplasty</t>
+    <t>myringoplastie</t>
   </si>
   <si>
     <t>397117006</t>
   </si>
   <si>
-    <t>Amputation of lower limb</t>
+    <t>amputation d'un membre inférieur</t>
   </si>
   <si>
     <t>397431004</t>
   </si>
   <si>
-    <t>Percutaneous transluminal coronary angioplasty with rotoablation, single vessel</t>
+    <t>angioplastie coronarienne transluminale percutanée par athérectomie rotationnelle, un seul vaisseau</t>
   </si>
   <si>
     <t>397516006</t>
   </si>
   <si>
-    <t>Photorefractive keratoplasty</t>
+    <t>kératectomie photoréfractive</t>
   </si>
   <si>
     <t>397760009</t>
   </si>
   <si>
-    <t>Tympanotomy</t>
+    <t>tympanotomie</t>
   </si>
   <si>
     <t>397956004</t>
@@ -2313,25 +2313,25 @@
     <t>398010007</t>
   </si>
   <si>
-    <t>Insertion of hip prosthesis</t>
+    <t>pose d'une prothèse de hanche</t>
   </si>
   <si>
     <t>398027004</t>
   </si>
   <si>
-    <t>Excision of varicose vein of lower limb</t>
+    <t>excision d'une varice du membre inférieur</t>
   </si>
   <si>
     <t>39845007</t>
   </si>
   <si>
-    <t>Anterior colporrhaphy</t>
+    <t>colporraphie antérieure</t>
   </si>
   <si>
     <t>398740003</t>
   </si>
   <si>
-    <t>Colostomy</t>
+    <t>colostomie</t>
   </si>
   <si>
     <t>399867007</t>
@@ -2343,253 +2343,253 @@
     <t>40059006</t>
   </si>
   <si>
-    <t>Creation of aortofemoral shunt</t>
+    <t>pontage aortofémoral</t>
   </si>
   <si>
     <t>40219000</t>
   </si>
   <si>
-    <t>Delivery by Malstrom's extraction with episiotomy</t>
+    <t>accouchement par extraction de Malmström avec épisiotomie</t>
   </si>
   <si>
     <t>40250003</t>
   </si>
   <si>
-    <t>Interatrial transposition of venous return</t>
+    <t>transposition interauriculaire de retour veineux</t>
   </si>
   <si>
     <t>405525004</t>
   </si>
   <si>
-    <t>Repair of aneurysm of abdominal aorta</t>
+    <t>réparation d'un anévrisme de l'aorte abdominale</t>
   </si>
   <si>
     <t>40654000</t>
   </si>
   <si>
-    <t>Operation on eyelid</t>
+    <t>opération de la paupière</t>
   </si>
   <si>
     <t>40862005</t>
   </si>
   <si>
-    <t>Local excision of skin and subcutaneous tissue</t>
+    <t>excision locale de la peau et du tissu sous-cutané</t>
   </si>
   <si>
     <t>408817009</t>
   </si>
   <si>
-    <t>Amniotomy at delivery</t>
+    <t>amniotomy at delivery</t>
   </si>
   <si>
     <t>41059002</t>
   </si>
   <si>
-    <t>Cesarean hysterectomy</t>
+    <t>césarienne-hystérectomie</t>
   </si>
   <si>
     <t>413144006</t>
   </si>
   <si>
-    <t>Abdominal hysterectomy with conservation of ovaries</t>
+    <t>hystérectomie abdominale avec conservation des ovaires</t>
   </si>
   <si>
     <t>41339005</t>
   </si>
   <si>
-    <t>Coronary angioplasty</t>
+    <t>angioplastie coronarienne</t>
   </si>
   <si>
     <t>414088005</t>
   </si>
   <si>
-    <t>Emergency CABG</t>
+    <t>pontage coronarien d'urgence</t>
   </si>
   <si>
     <t>41453009</t>
   </si>
   <si>
-    <t>Strabismus surgery</t>
+    <t>chirurgie pour strabisme</t>
   </si>
   <si>
     <t>414582004</t>
   </si>
   <si>
-    <t>Laser assisted subepithelial keratomileusis</t>
+    <t>kératomileusie sous-épithéliale au laser</t>
   </si>
   <si>
     <t>415070008</t>
   </si>
   <si>
-    <t>Percutaneous coronary intervention</t>
+    <t>intervention coronarienne percutanée</t>
   </si>
   <si>
     <t>41817002</t>
   </si>
   <si>
-    <t>Closure of patent foramen ovale</t>
+    <t>fermeture d'un foramen ovale persistant</t>
   </si>
   <si>
     <t>418285008</t>
   </si>
   <si>
-    <t>Angioplasty of blood vessel</t>
+    <t>angioplastie</t>
   </si>
   <si>
     <t>418576007</t>
   </si>
   <si>
-    <t>Harvesting of peripheral blood stem cells</t>
+    <t>prélèvement de cellules souches sanguines périphériques</t>
   </si>
   <si>
     <t>42101009</t>
   </si>
   <si>
-    <t>Penetrating keratoplasty</t>
+    <t>penetrating keratoplasty</t>
   </si>
   <si>
     <t>42262007</t>
   </si>
   <si>
-    <t>Total shoulder replacement</t>
+    <t>remplacement total de l'épaule</t>
   </si>
   <si>
     <t>423827005</t>
   </si>
   <si>
-    <t>Endoscopy</t>
+    <t>endoscopie</t>
   </si>
   <si>
     <t>425435003</t>
   </si>
   <si>
-    <t>Implantation of cardioverter defibrillator with one electrode lead</t>
+    <t>implantation d'un défibrillateur cardiaque muni d'une seule d'électrode</t>
   </si>
   <si>
     <t>426153007</t>
   </si>
   <si>
-    <t>Insertion of artificial airway</t>
+    <t>insertion d'un tube pharyngé</t>
   </si>
   <si>
     <t>427107006</t>
   </si>
   <si>
-    <t>Excision of accessory uterus</t>
+    <t>résection d'un utérus accessoire</t>
   </si>
   <si>
     <t>427508005</t>
   </si>
   <si>
-    <t>Implantation of cardioverter defibrillator with two electrode leads</t>
+    <t>implantation d'un défibrillateur cardiaque muni de deux électrodes</t>
   </si>
   <si>
     <t>427752004</t>
   </si>
   <si>
-    <t>Excision of lamina of lumbar vertebra for decompression of spinal cord</t>
+    <t>décompression médullaire par laminectomie lombaire</t>
   </si>
   <si>
     <t>427886002</t>
   </si>
   <si>
-    <t>Total cavopulmonary connection with lateral atrial tunnel</t>
+    <t>dérivation cavopulmonaire totale par tunnel latéral intra-atrial</t>
   </si>
   <si>
     <t>428613004</t>
   </si>
   <si>
-    <t>Correction of congenital cardiovascular deformity</t>
+    <t>correction d'une difformité congénitale cardiovasculaire</t>
   </si>
   <si>
     <t>428625001</t>
   </si>
   <si>
-    <t>Replacement of cardioverter defibrillator</t>
+    <t>remplacement d'un défibrillateur automatique</t>
   </si>
   <si>
     <t>428663009</t>
   </si>
   <si>
-    <t>Ablation of atrioventricular node</t>
+    <t>résection du nœud atrioventriculaire</t>
   </si>
   <si>
     <t>428989006</t>
   </si>
   <si>
-    <t>Operation on ganglion cyst</t>
+    <t>opération d'un kyste ganglionnaire</t>
   </si>
   <si>
     <t>429595007</t>
   </si>
   <si>
-    <t>Resection of neoplasm of heart</t>
+    <t>résection d'un néoplasme du cœur</t>
   </si>
   <si>
     <t>429616001</t>
   </si>
   <si>
-    <t>Aortopulmonary reconstruction with right ventricle to pulmonary arterial valveless conduit</t>
+    <t>reconstruction aortopulmonaire avec tube sans valve du ventricule droit à l'artère pulmonaire</t>
   </si>
   <si>
     <t>429620002</t>
   </si>
   <si>
-    <t>Construction of left ventricle to aorta tunnel with right ventricle to pulmonary artery valved conduit</t>
+    <t>construction d'un tunnel aorto-ventriculaire avec conduit valvulé entre le ventricule droit et l'artère pulmonaire</t>
   </si>
   <si>
     <t>429639007</t>
   </si>
   <si>
-    <t>Percutaneous transluminal balloon angioplasty with insertion of stent into coronary artery</t>
+    <t>angioplastie transluminale percutanée par ballonnet avec insertion d'une endoprothèse coronaire</t>
   </si>
   <si>
     <t>429653007</t>
   </si>
   <si>
-    <t>Repair of reducible inguinal hernia</t>
+    <t>traitement de hernie inguinale réductible</t>
   </si>
   <si>
     <t>430715008</t>
   </si>
   <si>
-    <t>Bariatric operative procedure</t>
+    <t>intervention chirurgicale bariatrique</t>
   </si>
   <si>
     <t>43075005</t>
   </si>
   <si>
-    <t>Partial resection of colon</t>
+    <t>colectomie partielle</t>
   </si>
   <si>
     <t>431339008</t>
   </si>
   <si>
-    <t>Mechanical prosthetic mitral valve replacement</t>
+    <t>remplacement d'une prothèse valvulaire mitrale mécanique</t>
   </si>
   <si>
     <t>432114008</t>
   </si>
   <si>
-    <t>Closure of atrial septal defect using fluoroscopic guidance</t>
+    <t>fermeture d'une communication interatriale guidée par fluoroscopie</t>
   </si>
   <si>
     <t>432394003</t>
   </si>
   <si>
-    <t>Repair of mitral valve using fluoroscopic guidance</t>
+    <t>réparation guidée par fluoroscopie de valvule mitrale</t>
   </si>
   <si>
     <t>432670006</t>
   </si>
   <si>
-    <t>Closure of patent foramen ovale using fluoroscopic guidance</t>
+    <t>fermeture du foramen ovale perméable guidée par fluoroscopie</t>
   </si>
   <si>
     <t>43815004</t>
   </si>
   <si>
-    <t>Implantation of cochlear prosthetic device, single channel</t>
+    <t>pose d'un implant cochléaire monocanal</t>
   </si>
   <si>
     <t>441612006</t>
@@ -2601,709 +2601,709 @@
     <t>441676000</t>
   </si>
   <si>
-    <t>Occlusion of patent ductus arteriosus using embolization coil</t>
+    <t>fermeture d'une persistance du canal artériel par microspires</t>
   </si>
   <si>
     <t>441873006</t>
   </si>
   <si>
-    <t>Percutaneous replacement of aortic valve using fluoroscopic guidance</t>
+    <t>remplacement valvulaire aortique percutané guidé par fluoroscopie</t>
   </si>
   <si>
     <t>442087005</t>
   </si>
   <si>
-    <t>Closure of ventricular septal defect using fluoroscopic guidance</t>
+    <t>fermeture d'une communication interventriculaire guidée par fluoroscopie</t>
   </si>
   <si>
     <t>442123009</t>
   </si>
   <si>
-    <t>Sano procedure</t>
+    <t>intervention de Sano</t>
   </si>
   <si>
     <t>44218004</t>
   </si>
   <si>
-    <t>Implantation of cochlear electrode</t>
+    <t>pose d'une électrode cochléaire</t>
   </si>
   <si>
     <t>442249009</t>
   </si>
   <si>
-    <t>Implantation of cardioverter defibrillator with three electrode leads</t>
+    <t>pose d'un défibrillateur cardiaque à trois électrodes</t>
   </si>
   <si>
     <t>44337006</t>
   </si>
   <si>
-    <t>Incision of gallbladder</t>
+    <t>incision de la vésicule biliaire</t>
   </si>
   <si>
     <t>443434006</t>
   </si>
   <si>
-    <t>Replacement of dual chamber pulse generator</t>
+    <t>remplacement d'un générateur d'implusions double chambre</t>
   </si>
   <si>
     <t>443681002</t>
   </si>
   <si>
-    <t>Total replacement of left knee joint</t>
+    <t>remplacement total de l'articulation du genou gauche</t>
   </si>
   <si>
     <t>443682009</t>
   </si>
   <si>
-    <t>Total replacement of right knee joint</t>
+    <t>remplacement total de l'articulation du genou droit</t>
   </si>
   <si>
     <t>44378008</t>
   </si>
   <si>
-    <t>Partial colectomy with anastomosis</t>
+    <t>colectomie partielle avec anastomose</t>
   </si>
   <si>
     <t>443829004</t>
   </si>
   <si>
-    <t>Percutaneous transluminal balloon angioplasty of coarctation of aorta with insertion of stent</t>
+    <t>angioplastie transluminale percutanée d'une coarctation de l'aorte par ballonnet avec pose d'une endoprothèse</t>
   </si>
   <si>
     <t>443887000</t>
   </si>
   <si>
-    <t>Transapical implantation of aortic valve</t>
+    <t>pose d'une valve aortique par voie transapicale</t>
   </si>
   <si>
     <t>443906008</t>
   </si>
   <si>
-    <t>Bypass of stomach with short limb Roux-en-Y gastroenterostomy</t>
+    <t>court-circuit gastrique par gastroentérostomie avec anse en Y de Roux courte</t>
   </si>
   <si>
     <t>443989003</t>
   </si>
   <si>
-    <t>Bidirectional Glenn shunt procedure of left superior vena cava</t>
+    <t>anastomose de Glenn bidirectionnelle de la veine cave supérieure gauche</t>
   </si>
   <si>
     <t>444001009</t>
   </si>
   <si>
-    <t>Right Glenn shunt procedure</t>
+    <t>anastomose cavopulmonaire de Glenn droite</t>
   </si>
   <si>
     <t>444034006</t>
   </si>
   <si>
-    <t>Bidirectional Glenn shunt procedure of right superior vena cava</t>
+    <t>anastomose de Glenn bidirectionnelle de la veine cave supérieure droite</t>
   </si>
   <si>
     <t>444178004</t>
   </si>
   <si>
-    <t>Left Glenn shunt procedure</t>
+    <t>anastomose cavopulmonaire de Glenn gauche</t>
   </si>
   <si>
     <t>444566006</t>
   </si>
   <si>
-    <t>Replacement of cardiac pacemaker</t>
+    <t>remplacement d'un stimulateur cardiaque</t>
   </si>
   <si>
     <t>444588006</t>
   </si>
   <si>
-    <t>Endovascular repair of abdominal aortic aneurysm</t>
+    <t>traitement endovasculaire d'un anévrisme de l'aorte abdominale</t>
   </si>
   <si>
     <t>445185007</t>
   </si>
   <si>
-    <t>Resurfacing of head of femur</t>
+    <t>resurfaçage de la tête du fémur</t>
   </si>
   <si>
     <t>445429009</t>
   </si>
   <si>
-    <t>Cervical laminectomy</t>
+    <t>laminectomie cervicale</t>
   </si>
   <si>
     <t>44558001</t>
   </si>
   <si>
-    <t>Repair of inguinal hernia</t>
+    <t>réparation d'une hernie inguinale</t>
   </si>
   <si>
     <t>44777001</t>
   </si>
   <si>
-    <t>Creation of conduit between right ventricle and pulmonary artery</t>
+    <t>création d'un shunt entre le ventricule droit et d'une artère pulmonaire</t>
   </si>
   <si>
     <t>449389000</t>
   </si>
   <si>
-    <t>Placement of stent in cardiac conduit</t>
+    <t>pose d'une endoprothèse dans un conduit cardiaque</t>
   </si>
   <si>
     <t>44946007</t>
   </si>
   <si>
-    <t>Repair of umbilical hernia</t>
+    <t>réparation d'une hernie ombilicale</t>
   </si>
   <si>
     <t>450350009</t>
   </si>
   <si>
-    <t>Primary repair of cleft palate</t>
+    <t>réparation primaire d'une fente palatine</t>
   </si>
   <si>
     <t>45595009</t>
   </si>
   <si>
-    <t>Laparoscopic cholecystectomy</t>
+    <t>cholécystectomie par laparoscopie</t>
   </si>
   <si>
     <t>45681003</t>
   </si>
   <si>
-    <t>Incision, exploration and biopsy for determination of stage of disease</t>
+    <t>incision, exploration et biopsie pour détermination du stade d'une pathologie</t>
   </si>
   <si>
     <t>45921003</t>
   </si>
   <si>
-    <t>Removal of cardiac pacemaker electrodes with replacement</t>
+    <t>retrait et remplacement d'électrodes d'un stimulateur cardiaque</t>
   </si>
   <si>
     <t>45993005</t>
   </si>
   <si>
-    <t>Cholecystectomy with exploration of common duct</t>
+    <t>cholécystectomie avec exploration du canal cholédoque</t>
   </si>
   <si>
     <t>46116005</t>
   </si>
   <si>
-    <t>Excision of malignant tumor of breast</t>
+    <t>excision d'un néoplasme malin d'un sein</t>
   </si>
   <si>
     <t>46681009</t>
   </si>
   <si>
-    <t>Cerclage of cervix during pregnancy by abdominal approach</t>
+    <t>cerclage du col de l'utérus pendant la grossesse par voie abdominale</t>
   </si>
   <si>
     <t>47020004</t>
   </si>
   <si>
-    <t>Ventriculoperitoneal shunt</t>
+    <t>DVP - dérivation ventriculopéritonéale</t>
   </si>
   <si>
     <t>47411002</t>
   </si>
   <si>
-    <t>Insertion of penile prosthesis</t>
+    <t>pose d'une prothèse pénienne</t>
   </si>
   <si>
     <t>47432005</t>
   </si>
   <si>
-    <t>Implantation of heart valve prosthesis or synthetic device</t>
+    <t>pose d'une valvule cardiaque prothétique ou artificielle</t>
   </si>
   <si>
     <t>47534009</t>
   </si>
   <si>
-    <t>Decompression of median nerve</t>
+    <t>décompression du nerf médian</t>
   </si>
   <si>
     <t>4770005</t>
   </si>
   <si>
-    <t>Colporrhaphy for repair of urethrocele</t>
+    <t>colporraphie pour traitement de l'urétrocèle</t>
   </si>
   <si>
     <t>48387007</t>
   </si>
   <si>
-    <t>Incision of trachea</t>
+    <t>incision de la trachée</t>
   </si>
   <si>
     <t>48835001</t>
   </si>
   <si>
-    <t>Esophagogastric fundoplasty</t>
+    <t>fundoplastie œsogastrique</t>
   </si>
   <si>
     <t>49209004</t>
   </si>
   <si>
-    <t>Subtotal gastrectomy</t>
+    <t>gastrectomie partielle</t>
   </si>
   <si>
     <t>49509003</t>
   </si>
   <si>
-    <t>Operation on lymphatic structure</t>
+    <t>intervention chirurgicale sur le système lymphatique</t>
   </si>
   <si>
     <t>49795001</t>
   </si>
   <si>
-    <t>Total pneumonectomy</t>
+    <t>pneumonectomie simple</t>
   </si>
   <si>
     <t>50172003</t>
   </si>
   <si>
-    <t>Lumbar spinal fusion</t>
+    <t>arthrodèse lombaire</t>
   </si>
   <si>
     <t>50216001</t>
   </si>
   <si>
-    <t>Replacement of mitral valve with tissue graft</t>
+    <t>remplacement valvulaire mitral par greffe tissulaire</t>
   </si>
   <si>
     <t>50445001</t>
   </si>
   <si>
-    <t>Mastoidectomy</t>
+    <t>mastoïdectomie</t>
   </si>
   <si>
     <t>50465008</t>
   </si>
   <si>
-    <t>Hernia repair</t>
+    <t>cure de hernie</t>
   </si>
   <si>
     <t>50590007</t>
   </si>
   <si>
-    <t>Trephine biopsy</t>
+    <t>biopsie au trépan</t>
   </si>
   <si>
     <t>50676004</t>
   </si>
   <si>
-    <t>Implantation of cochlear prosthetic device, multiple channels</t>
+    <t>pose d'un implant cochléaire multicanal</t>
   </si>
   <si>
     <t>50807007</t>
   </si>
   <si>
-    <t>Femoral-popliteal artery bypass graft with vein</t>
+    <t>pontage artériel fémoropoplité par greffe veineuse</t>
   </si>
   <si>
     <t>51683002</t>
   </si>
   <si>
-    <t>Radial keratotomy</t>
+    <t>kératotomie radiaire</t>
   </si>
   <si>
     <t>52247003</t>
   </si>
   <si>
-    <t>Repair of aortic valve with tissue graft</t>
+    <t>remplacement de la valve aortique par bioprothèse</t>
   </si>
   <si>
     <t>52660002</t>
   </si>
   <si>
-    <t>Induced termination of pregnancy following intra-amniotic injection with hysterotomy</t>
+    <t>avortement provoqué avec injection intra-amniotique et hystérotomie</t>
   </si>
   <si>
     <t>52734007</t>
   </si>
   <si>
-    <t>Total replacement of hip</t>
+    <t>implantation d'une prothèse totale de hanche</t>
   </si>
   <si>
     <t>52852000</t>
   </si>
   <si>
-    <t>Insertion of bilateral breast prostheses</t>
+    <t>pose bilatérale de prothèses mammaires</t>
   </si>
   <si>
     <t>53059001</t>
   </si>
   <si>
-    <t>Replacement of mitral valve</t>
+    <t>remplacement de la valve mitrale</t>
   </si>
   <si>
     <t>53266006</t>
   </si>
   <si>
-    <t>Operation on diaphragm</t>
+    <t>intervention chirurgicale du diaphragme</t>
   </si>
   <si>
     <t>53304009</t>
   </si>
   <si>
-    <t>Parathyroidectomy</t>
+    <t>parathyroïdectomie</t>
   </si>
   <si>
     <t>53442002</t>
   </si>
   <si>
-    <t>Gastrectomy</t>
+    <t>gastrectomie</t>
   </si>
   <si>
     <t>53610001</t>
   </si>
   <si>
-    <t>Nasal septoplasty with graft</t>
+    <t>septoplastie nasale avec greffe</t>
   </si>
   <si>
     <t>53958007</t>
   </si>
   <si>
-    <t>Harvesting of donor material</t>
+    <t>prélèvement de tissu</t>
   </si>
   <si>
     <t>53976000</t>
   </si>
   <si>
-    <t>Arthrodesis by anterior interbody technique of cervical region below C2 with bone graft</t>
+    <t>arthrodèse intercorporéale par voie antérieure de la région cervicale en-dessous de C2 avec greffe osseuse</t>
   </si>
   <si>
     <t>54261007</t>
   </si>
   <si>
-    <t>Excision of uterus and supporting structures</t>
+    <t>ablation de l'utérus et des structures de soutien</t>
   </si>
   <si>
     <t>54535009</t>
   </si>
   <si>
-    <t>Cone biopsy of cervix</t>
+    <t>conisation du col utérin</t>
   </si>
   <si>
     <t>54866009</t>
   </si>
   <si>
-    <t>Initial implantation of cardiac single-chamber device</t>
+    <t>implantation initiale d'un dispositif cardiaque monochambre</t>
   </si>
   <si>
     <t>54885007</t>
   </si>
   <si>
-    <t>Extraction of cataract</t>
+    <t>extraction d'une cataracte</t>
   </si>
   <si>
     <t>54956002</t>
   </si>
   <si>
-    <t>Gastrostomy</t>
+    <t>gastrostomie</t>
   </si>
   <si>
     <t>54974006</t>
   </si>
   <si>
-    <t>Insertion of permanent pacemaker with transvenous electrodes, ventricular</t>
+    <t>insertion d'un stimulateur permanent avec électrodes endoveineuses, ventriculaire</t>
   </si>
   <si>
     <t>55244002</t>
   </si>
   <si>
-    <t>Arthroscopically aided anterior cruciate ligament repair</t>
+    <t>réparation du ligament croisé antérieur sous arthroscopie</t>
   </si>
   <si>
     <t>55253009</t>
   </si>
   <si>
-    <t>Replacement of tricuspid valve with tissue graft</t>
+    <t>remplacement de valve tricuspide avec greffe tissulaire</t>
   </si>
   <si>
     <t>55705006</t>
   </si>
   <si>
-    <t>Spinal arthrodesis</t>
+    <t>arthrodèse du rachis</t>
   </si>
   <si>
     <t>56060000</t>
   </si>
   <si>
-    <t>Repair of musculotendinous cuff of shoulder</t>
+    <t>réparation de la coiffe des rotateurs</t>
   </si>
   <si>
     <t>56062008</t>
   </si>
   <si>
-    <t>Repair of sliding inguinal hernia</t>
+    <t>traitement de hernie inguinale par glissement</t>
   </si>
   <si>
     <t>56283009</t>
   </si>
   <si>
-    <t>Transplantation of small intestine</t>
+    <t>transplantation de l'intestin grêle</t>
   </si>
   <si>
     <t>56306000</t>
   </si>
   <si>
-    <t>Cosmetic surgery</t>
+    <t>chirurgie esthétique</t>
   </si>
   <si>
     <t>56361007</t>
   </si>
   <si>
-    <t>Excision of soft tissue</t>
+    <t>excision de tissu mou</t>
   </si>
   <si>
     <t>56757003</t>
   </si>
   <si>
-    <t>Scraping</t>
+    <t>grattage</t>
   </si>
   <si>
     <t>56783008</t>
   </si>
   <si>
-    <t>Incision AND drainage</t>
+    <t>incision et drainage</t>
   </si>
   <si>
     <t>57168000</t>
   </si>
   <si>
-    <t>Operation on bone</t>
+    <t>intervention chirurgicale d'un os</t>
   </si>
   <si>
     <t>57217008</t>
   </si>
   <si>
-    <t>Thompson operation, cleft lip repair</t>
+    <t>intervention chirurgicale de Thompson, réparation d'une fente labiale</t>
   </si>
   <si>
     <t>57271003</t>
   </si>
   <si>
-    <t>Extraperitoneal cesarean section</t>
+    <t>césarienne extrapéritonéale</t>
   </si>
   <si>
     <t>57411006</t>
   </si>
   <si>
-    <t>Colpoperineorrhaphy following delivery</t>
+    <t>colpopérinéorraphie après accouchement</t>
   </si>
   <si>
     <t>5781000</t>
   </si>
   <si>
-    <t>Operation on nasal septum</t>
+    <t>opération du septum nasal</t>
   </si>
   <si>
     <t>58863009</t>
   </si>
   <si>
-    <t>Initial implantation of cardiac dual-chamber device</t>
+    <t>implantation initiale d'un dispositif cardiaque double chambre</t>
   </si>
   <si>
     <t>59213002</t>
   </si>
   <si>
-    <t>Repair of ruptured supraspinatus tendon, acute</t>
+    <t>réparation d'une rupture aigüe du tendon supraépineux</t>
   </si>
   <si>
     <t>59214008</t>
   </si>
   <si>
-    <t>Reduction mammoplasty</t>
+    <t>mammoplastie de réduction</t>
   </si>
   <si>
     <t>59300005</t>
   </si>
   <si>
-    <t>Operation on spleen</t>
+    <t>intervention chirurgicale de la rate</t>
   </si>
   <si>
     <t>59657005</t>
   </si>
   <si>
-    <t>Intestinal bypass for morbid obesity</t>
+    <t>bypass intestinal pour obésité morbide</t>
   </si>
   <si>
     <t>59703009</t>
   </si>
   <si>
-    <t>Cervical arthrodesis by anterior technique</t>
+    <t>fusion de la colonne cervicale par technique antérieure</t>
   </si>
   <si>
     <t>59712006</t>
   </si>
   <si>
-    <t>Evacuation of subdural hematoma</t>
+    <t>évacuation d'un hématome sous-dural</t>
   </si>
   <si>
     <t>6025007</t>
   </si>
   <si>
-    <t>Laparoscopic appendectomy</t>
+    <t>appendicectomie par laparoscopie</t>
   </si>
   <si>
     <t>60656008</t>
   </si>
   <si>
-    <t>Corneal transplant</t>
+    <t>greffe cornéenne</t>
   </si>
   <si>
     <t>609588000</t>
   </si>
   <si>
-    <t>Total knee replacement</t>
+    <t>remplacement total du genou</t>
   </si>
   <si>
     <t>61498008</t>
   </si>
   <si>
-    <t>Complete external hemorrhoidectomy</t>
+    <t>hémorroïdectomie externe complète</t>
   </si>
   <si>
     <t>61661004</t>
   </si>
   <si>
-    <t>Operative procedure on foot</t>
+    <t>intervention chirurgicale sur le pied</t>
   </si>
   <si>
     <t>61774002</t>
   </si>
   <si>
-    <t>Repair of rotator cuff by suture</t>
+    <t>réparation par suture de la coiffe des rotateurs</t>
   </si>
   <si>
     <t>62141006</t>
   </si>
   <si>
-    <t>Radical excision</t>
+    <t>éxérèse radicale</t>
   </si>
   <si>
     <t>6240004</t>
   </si>
   <si>
-    <t>Operative procedure on knee</t>
+    <t>intervention chirurgicale du genou</t>
   </si>
   <si>
     <t>62438007</t>
   </si>
   <si>
-    <t>Transplantation of pancreas</t>
+    <t>transplantation du pancréas</t>
   </si>
   <si>
     <t>62881002</t>
   </si>
   <si>
-    <t>Removal of cardiac pacemaker</t>
+    <t>retrait d'un stimulateur cardiaque</t>
   </si>
   <si>
     <t>63016009</t>
   </si>
   <si>
-    <t>Complete cystectomy</t>
+    <t>cystectomie totale</t>
   </si>
   <si>
     <t>63697000</t>
   </si>
   <si>
-    <t>Cardiopulmonary bypass operation</t>
+    <t>pontage cardiopulmonaire</t>
   </si>
   <si>
     <t>64253000</t>
   </si>
   <si>
-    <t>Implantation of heart assist system</t>
+    <t>implantation d'un système d'assistance cardiaque</t>
   </si>
   <si>
     <t>64368001</t>
   </si>
   <si>
-    <t>Partial mastectomy</t>
+    <t>mastectomie partielle</t>
   </si>
   <si>
     <t>64915003</t>
   </si>
   <si>
-    <t>Operation on heart</t>
+    <t>intervention chirurgicale du cœur</t>
   </si>
   <si>
     <t>64978007</t>
   </si>
   <si>
-    <t>Radionuclide therapy for hyperthyroidism</t>
+    <t>traitement radio-isotopique de l'hyperthyroïdie</t>
   </si>
   <si>
     <t>65551008</t>
   </si>
   <si>
-    <t>Radical retropubic prostatectomy</t>
+    <t>prostatectomie rétropubienne totale</t>
   </si>
   <si>
     <t>65659003</t>
   </si>
   <si>
-    <t>Rotational atherectomy</t>
+    <t>athérectomie rotationnelle</t>
   </si>
   <si>
     <t>65801008</t>
   </si>
   <si>
-    <t>Excision</t>
+    <t>excision</t>
   </si>
   <si>
     <t>65854006</t>
   </si>
   <si>
-    <t>Reexcision</t>
+    <t>réexcision</t>
   </si>
   <si>
     <t>66692001</t>
   </si>
   <si>
-    <t>Repair of ruptured supraspinatus tendon, chronic</t>
+    <t>réparation d'une rupture chronique du tendon supraépineux</t>
   </si>
   <si>
     <t>66951008</t>
   </si>
   <si>
-    <t>Carotid endarterectomy</t>
+    <t>endartériectomie d'une carotide</t>
   </si>
   <si>
     <t>67557008</t>
   </si>
   <si>
-    <t>Laparoscopic cholecystectomy with exploration of common duct</t>
+    <t>cholécystectomie laparoscopique avec exploration du canal cholédoque</t>
   </si>
   <si>
     <t>68265005</t>
   </si>
   <si>
-    <t>Operation on the ear</t>
+    <t>opération de l'oreille</t>
   </si>
   <si>
     <t>6832004</t>
   </si>
   <si>
-    <t>Atherectomy</t>
+    <t>athérectomie</t>
   </si>
   <si>
     <t>68457009</t>
   </si>
   <si>
-    <t>Percutaneous transluminal balloon angioplasty</t>
+    <t>angioplastie transluminale percutanée par ballonnet</t>
   </si>
   <si>
     <t>68660007</t>
   </si>
   <si>
-    <t>Punch biopsy</t>
+    <t>biopsie à l'emporte-pièce</t>
   </si>
   <si>
     <t>68792000</t>
   </si>
   <si>
-    <t>Wardill operation, cleft palate repair</t>
+    <t>opération de Wardill, réparation d'une fente palatine</t>
   </si>
   <si>
     <t>69031006</t>
@@ -3315,529 +3315,529 @@
     <t>69130005</t>
   </si>
   <si>
-    <t>Stapedectomy</t>
+    <t>stapédectomie</t>
   </si>
   <si>
     <t>69724002</t>
   </si>
   <si>
-    <t>Insertion of intraocular lens</t>
+    <t>insertion d'une lentille intraoculaire</t>
   </si>
   <si>
     <t>70183006</t>
   </si>
   <si>
-    <t>Subcutaneous mastectomy</t>
+    <t>mastectomie sous-cutanée</t>
   </si>
   <si>
     <t>70536003</t>
   </si>
   <si>
-    <t>Transplant of kidney</t>
+    <t>greffe rénale</t>
   </si>
   <si>
     <t>70871006</t>
   </si>
   <si>
-    <t>Incisional biopsy</t>
+    <t>biopsie incisionnelle</t>
   </si>
   <si>
     <t>72010008</t>
   </si>
   <si>
-    <t>Removal of internal fixation device</t>
+    <t>retrait d'un dispositif d'ostéosynthèse interne</t>
   </si>
   <si>
     <t>72310004</t>
   </si>
   <si>
-    <t>Circumcision</t>
+    <t>circoncision</t>
   </si>
   <si>
     <t>72342005</t>
   </si>
   <si>
-    <t>Shave biopsy</t>
+    <t>biopsie par rasage</t>
   </si>
   <si>
     <t>726429001</t>
   </si>
   <si>
-    <t>Radical mastectomy of left breast</t>
+    <t>mastectomie radicale du sein gauche</t>
   </si>
   <si>
     <t>726430006</t>
   </si>
   <si>
-    <t>Radical mastectomy of right breast</t>
+    <t>mastectomie radicale du sein droit</t>
   </si>
   <si>
     <t>726436000</t>
   </si>
   <si>
-    <t>Modified radical mastectomy of right breast</t>
+    <t>mastectomie radicale modifiée du sein droit</t>
   </si>
   <si>
     <t>726437009</t>
   </si>
   <si>
-    <t>Modified radical mastectomy of left breast</t>
+    <t>mastectomie radicale modifiée du sein gauche</t>
   </si>
   <si>
     <t>72791001</t>
   </si>
   <si>
-    <t>Laryngectomy</t>
+    <t>laryngectomie</t>
   </si>
   <si>
     <t>735023007</t>
   </si>
   <si>
-    <t>Fixation of left testis</t>
+    <t>fixation du testicule gauche</t>
   </si>
   <si>
     <t>735024001</t>
   </si>
   <si>
-    <t>Fixation of right testis</t>
+    <t>fixation du testicule droit</t>
   </si>
   <si>
     <t>73544002</t>
   </si>
   <si>
-    <t>Operation on heart valve</t>
+    <t>intervention chirurgicale d'une valve cardiaque</t>
   </si>
   <si>
     <t>73761001</t>
   </si>
   <si>
-    <t>Colonoscopy</t>
+    <t>colonoscopie</t>
   </si>
   <si>
     <t>74770008</t>
   </si>
   <si>
-    <t>Exploratory laparotomy</t>
+    <t>laparotomie exploratoire</t>
   </si>
   <si>
     <t>75170007</t>
   </si>
   <si>
-    <t>Extraction of lens of eye</t>
+    <t>extraction du cristallin</t>
   </si>
   <si>
     <t>75732000</t>
   </si>
   <si>
-    <t>Vitrectomy</t>
+    <t>vitrectomie</t>
   </si>
   <si>
     <t>76025005</t>
   </si>
   <si>
-    <t>Correction of ventricular septal defect</t>
+    <t>correction d'une communication interventriculaire</t>
   </si>
   <si>
     <t>76611008</t>
   </si>
   <si>
-    <t>Atherectomy by laser</t>
+    <t>athérectomie au laser</t>
   </si>
   <si>
     <t>76810006</t>
   </si>
   <si>
-    <t>Diagnostic dilation and curettage of uterus</t>
+    <t>dilatation et curetage de l'utérus pour fin de diagnostic</t>
   </si>
   <si>
     <t>76956004</t>
   </si>
   <si>
-    <t>Amputation of finger, except thumb</t>
+    <t>amputation d'un doigt, sauf le pouce</t>
   </si>
   <si>
     <t>771453009</t>
   </si>
   <si>
-    <t>Repair of abdominal aortic aneurysm with insertion of stent</t>
+    <t>réparation avec pose de stent d'anévrisme aortique abdominal</t>
   </si>
   <si>
     <t>77166000</t>
   </si>
   <si>
-    <t>Percutaneous balloon valvuloplasty of aortic valve</t>
+    <t>valvuloplastie aortique percutanée par ballonnet</t>
   </si>
   <si>
     <t>77181006</t>
   </si>
   <si>
-    <t>Implantation of mitral valve prosthesis or synthetic device</t>
+    <t>pose de valve mitrale prothétique ou artificielle</t>
   </si>
   <si>
     <t>77543007</t>
   </si>
   <si>
-    <t>Ligation of fallopian tube</t>
+    <t>ligature d'un salpinx</t>
   </si>
   <si>
     <t>78418002</t>
   </si>
   <si>
-    <t>Operation on heart and pericardium</t>
+    <t>intervention chirurgicale du cœur et du péricarde</t>
   </si>
   <si>
     <t>78559005</t>
   </si>
   <si>
-    <t>Operative procedure on shoulder</t>
+    <t>intervention chirurgicale de la région de l'épaule</t>
   </si>
   <si>
     <t>79095000</t>
   </si>
   <si>
-    <t>Complete excision</t>
+    <t>excision totale</t>
   </si>
   <si>
     <t>79733001</t>
   </si>
   <si>
-    <t>Amputation above-knee</t>
+    <t>amputation au-dessus du genou</t>
   </si>
   <si>
     <t>79917009</t>
   </si>
   <si>
-    <t>Implantation of pulmonary valve prosthesis or synthetic device</t>
+    <t>pose de valve pulmonaire prothétique ou artificielle</t>
   </si>
   <si>
     <t>80146002</t>
   </si>
   <si>
-    <t>Appendectomy</t>
+    <t>appendicectomie</t>
   </si>
   <si>
     <t>8069005</t>
   </si>
   <si>
-    <t>Implantation of tricuspid valve prosthesis or synthetic device</t>
+    <t>pose de valve tricuspide prothétique ou artificielle</t>
   </si>
   <si>
     <t>81099000</t>
   </si>
   <si>
-    <t>Cervical arthrodesis</t>
+    <t>fusion de la colonne cervicale</t>
   </si>
   <si>
     <t>81516001</t>
   </si>
   <si>
-    <t>Partial nephrectomy</t>
+    <t>néphrectomie partielle</t>
   </si>
   <si>
     <t>81723002</t>
   </si>
   <si>
-    <t>Amputation</t>
+    <t>amputation</t>
   </si>
   <si>
     <t>81870009</t>
   </si>
   <si>
-    <t>Parotidectomy</t>
+    <t>parotidectomie</t>
   </si>
   <si>
     <t>82035006</t>
   </si>
   <si>
-    <t>Resection of polyp</t>
+    <t>résection d'un polype</t>
   </si>
   <si>
     <t>83152002</t>
   </si>
   <si>
-    <t>Oophorectomy</t>
+    <t>excision de l'ovaire</t>
   </si>
   <si>
     <t>83333004</t>
   </si>
   <si>
-    <t>Creation of cardiac pacemaker pocket new site in subcutaneous tissue</t>
+    <t>création d'un nouveau site de poche de stimulateur cardiaque dans le tissu subcutané</t>
   </si>
   <si>
     <t>8378006</t>
   </si>
   <si>
-    <t>Trimming</t>
+    <t>parage</t>
   </si>
   <si>
     <t>84088001</t>
   </si>
   <si>
-    <t>Correction of atresia of external meatus of ear</t>
+    <t>traitement d'atrésie du méat de l'oreille externe</t>
   </si>
   <si>
     <t>84149000</t>
   </si>
   <si>
-    <t>Aspiration of cataract by phacoemulsification</t>
+    <t>aspiration de cataracte par phacoémulsification</t>
   </si>
   <si>
     <t>84195007</t>
   </si>
   <si>
-    <t>Classical cesarean section</t>
+    <t>césarienne traditionnelle</t>
   </si>
   <si>
     <t>8422009</t>
   </si>
   <si>
-    <t>Destruction of hemorrhoids by sclerotherapy</t>
+    <t>sclérothérapie des hémorroïdes</t>
   </si>
   <si>
     <t>84267003</t>
   </si>
   <si>
-    <t>Hysterotomy with removal of foreign body</t>
+    <t>hystérotomie avec extraction d'un corps étranger</t>
   </si>
   <si>
     <t>84275009</t>
   </si>
   <si>
-    <t>Obstetrical hysterotomy</t>
+    <t>hystérotomie obstétricale</t>
   </si>
   <si>
     <t>84282008</t>
   </si>
   <si>
-    <t>Hemorrhoidectomy by simple ligature</t>
+    <t>ligature d'hémorroïdes</t>
   </si>
   <si>
     <t>84877006</t>
   </si>
   <si>
-    <t>Arthroscopy of knee with meniscus repair</t>
+    <t>arthroscopie du genou avec réparation du ménisque</t>
   </si>
   <si>
     <t>85419002</t>
   </si>
   <si>
-    <t>Orchidopexy</t>
+    <t>orchidopexie</t>
   </si>
   <si>
     <t>85548006</t>
   </si>
   <si>
-    <t>Episiotomy</t>
+    <t>épisiotomie</t>
   </si>
   <si>
     <t>85921004</t>
   </si>
   <si>
-    <t>Puncture procedure</t>
+    <t>ponction</t>
   </si>
   <si>
     <t>8616005</t>
   </si>
   <si>
-    <t>Rhinocheiloplasty repair for cleft lip</t>
+    <t>rhinochéiloplastie d'une fente labiale</t>
   </si>
   <si>
     <t>86273004</t>
   </si>
   <si>
-    <t>Biopsy</t>
+    <t>biopsie</t>
   </si>
   <si>
     <t>86477000</t>
   </si>
   <si>
-    <t>Total hysterectomy with removal of both tubes and ovaries</t>
+    <t>hystérectomie totale avec ablation des deux trompes et des ovaires</t>
   </si>
   <si>
     <t>86480004</t>
   </si>
   <si>
-    <t>Open reduction of fracture</t>
+    <t>réduction ouverte d'une fracture</t>
   </si>
   <si>
     <t>86481000</t>
   </si>
   <si>
-    <t>Laparotomy</t>
+    <t>laparotomie</t>
   </si>
   <si>
     <t>86743009</t>
   </si>
   <si>
-    <t>Local excision</t>
+    <t>résection locale</t>
   </si>
   <si>
     <t>86749008</t>
   </si>
   <si>
-    <t>Stripping and ligation</t>
+    <t>stripping et ligature</t>
   </si>
   <si>
     <t>86800006</t>
   </si>
   <si>
-    <t>Operation on trachea</t>
+    <t>intervention chirurgicale du trachée</t>
   </si>
   <si>
     <t>87021001</t>
   </si>
   <si>
-    <t>Mechanical vitrectomy by pars plana approach</t>
+    <t>vitrectomie mécanique par la pars plana</t>
   </si>
   <si>
     <t>87366001</t>
   </si>
   <si>
-    <t>Total elbow replacement</t>
+    <t>arthroplastie prothétique totale du coude</t>
   </si>
   <si>
     <t>87795007</t>
   </si>
   <si>
-    <t>Complete transurethral resection of prostate, including control of postoperative bleeding</t>
+    <t>résection transurétrale complète de la prostate avec contrôle d'une hémorragie postopératoire</t>
   </si>
   <si>
     <t>8782006</t>
   </si>
   <si>
-    <t>Radical perineal prostatectomy</t>
+    <t>prostatectomie périnéale totale</t>
   </si>
   <si>
     <t>87825006</t>
   </si>
   <si>
-    <t>Initial implantation of electrode into cardiac atrium and ventricle</t>
+    <t>implantation initiale d'une électrode dans une oreillette et un ventricule cardiaque</t>
   </si>
   <si>
     <t>88039007</t>
   </si>
   <si>
-    <t>Transplant of lung</t>
+    <t>greffe pulmonaire</t>
   </si>
   <si>
     <t>88088007</t>
   </si>
   <si>
-    <t>Radical excision with lymph node dissection</t>
+    <t>excision radicale avec lymphadénectomie</t>
   </si>
   <si>
     <t>88312006</t>
   </si>
   <si>
-    <t>Amputation of leg through tibia and fibula</t>
+    <t>amputation de la jambe sous le genou</t>
   </si>
   <si>
     <t>88722002</t>
   </si>
   <si>
-    <t>Initial implantation of electrode into cardiac atrium</t>
+    <t>implantation initiale d'une électrode dans un atrium du cœur</t>
   </si>
   <si>
     <t>8874001</t>
   </si>
   <si>
-    <t>Arthroscopy of knee with medial and lateral meniscectomy</t>
+    <t>arthroscopie d'un genou avec méniscectomie médiale et latérale</t>
   </si>
   <si>
     <t>8889005</t>
   </si>
   <si>
-    <t>Excisional biopsy</t>
+    <t>biopsie-exérèse</t>
   </si>
   <si>
     <t>89053004</t>
   </si>
   <si>
-    <t>Vaginal cesarean section</t>
+    <t>césarienne vaginale</t>
   </si>
   <si>
     <t>8920006</t>
   </si>
   <si>
-    <t>Repair of retina for retinal detachment</t>
+    <t>réparation d'un décollement rétinien</t>
   </si>
   <si>
     <t>89355001</t>
   </si>
   <si>
-    <t>Discectomy for intervertebral herniated disc, nucleus pulposus</t>
+    <t>discectomie pour hernie discale intervertébrale, nucleus pulposus</t>
   </si>
   <si>
     <t>89432003</t>
   </si>
   <si>
-    <t>Lemesurier operation, cleft lip repair</t>
+    <t>opération de Lemesurier, réparation d'une fente labiale</t>
   </si>
   <si>
     <t>89540006</t>
   </si>
   <si>
-    <t>Segmental excision and ligation</t>
+    <t>résection segmentaire et ligature</t>
   </si>
   <si>
     <t>89814007</t>
   </si>
   <si>
-    <t>Repair of ventricular septal defect with prosthesis</t>
+    <t>fermeture d'une communication interventriculaire par prothèse</t>
   </si>
   <si>
     <t>90199006</t>
   </si>
   <si>
-    <t>Transurethral prostatectomy</t>
+    <t>prostatectomie transurétrale</t>
   </si>
   <si>
     <t>90442009</t>
   </si>
   <si>
-    <t>Cerclage of cervix during pregnancy by vaginal approach</t>
+    <t>cerclage du col utérin par voie vaginale pendant une grossesse</t>
   </si>
   <si>
     <t>90470006</t>
   </si>
   <si>
-    <t>Prostatectomy</t>
+    <t>prostatectomie</t>
   </si>
   <si>
     <t>9888007</t>
   </si>
   <si>
-    <t>Excision of intracranial lesion</t>
+    <t>excision d'une lésion intracrânienne</t>
   </si>
   <si>
     <t>2598006</t>
   </si>
   <si>
-    <t>Open heart surgery</t>
+    <t>intervention chirurgicale à cœur ouvert</t>
   </si>
   <si>
     <t>6148000</t>
   </si>
   <si>
-    <t>Chondrectomy of semilunar cartilage of knee</t>
+    <t>méniscectomie</t>
   </si>
   <si>
     <t>6976007</t>
   </si>
   <si>
-    <t>Craniocervical spinal fusion</t>
+    <t>arthrodèse crânio-cervicale</t>
   </si>
   <si>
     <t>10836008</t>
   </si>
   <si>
-    <t>Decompression of spinal cord</t>
+    <t>décompression de la moelle spinale</t>
   </si>
   <si>
     <t>11291002</t>
   </si>
   <si>
-    <t>Excision of lesion of omentum</t>
+    <t>résection de lésion de l'omentum</t>
   </si>
   <si>
     <t>12745006</t>
@@ -3849,589 +3849,583 @@
     <t>21525004</t>
   </si>
   <si>
-    <t>Excision of regional lymph nodes</t>
+    <t>exérèse de nœuds lymphatiques régionaux</t>
   </si>
   <si>
     <t>23580000</t>
   </si>
   <si>
-    <t>Hemisection of tooth</t>
+    <t>hémisection de dent</t>
   </si>
   <si>
     <t>25789004</t>
   </si>
   <si>
-    <t>Lumbosacral arthrodesis</t>
+    <t>arthrodèse lombosacrée</t>
   </si>
   <si>
     <t>25811000</t>
   </si>
   <si>
-    <t>Bilateral complete salpingectomy</t>
+    <t>salpingectomie bilatérale totale</t>
   </si>
   <si>
     <t>29672006</t>
   </si>
   <si>
-    <t>Partial oophorectomy</t>
+    <t>ovariectomie partielle</t>
   </si>
   <si>
     <t>31501000</t>
   </si>
   <si>
-    <t>Ethmoid sinusectomy</t>
+    <t>sinusectomie ethmoïdale</t>
   </si>
   <si>
     <t>34238000</t>
   </si>
   <si>
-    <t>Lumbar and lumbosacral fusion by posterior technique</t>
+    <t>arthrodèse lombaire et lombosacrée postérieure</t>
   </si>
   <si>
     <t>37053006</t>
   </si>
   <si>
-    <t>Open reduction of fracture of humerus with internal fixation</t>
+    <t>réduction ouverte d'une fracture de l'humérus avec ostéosynthèse interne</t>
   </si>
   <si>
     <t>44119001</t>
   </si>
   <si>
-    <t>Anastomosis of small intestine to small intestine</t>
+    <t>anastomose de l'intestin grêle à l'instestin grêle</t>
   </si>
   <si>
     <t>44166002</t>
   </si>
   <si>
-    <t>Radical excision of skin lesion</t>
+    <t>exérèse totale de lésion cutanée</t>
   </si>
   <si>
     <t>49273004</t>
   </si>
   <si>
-    <t>Laparoscopy with removal of adnexal structures</t>
+    <t>laparoscopie avec retrait des structures annexielles</t>
   </si>
   <si>
     <t>51302004</t>
   </si>
   <si>
-    <t>Turbinectomy</t>
+    <t>turbinectomie</t>
   </si>
   <si>
     <t>54357003</t>
   </si>
   <si>
-    <t>Partial excision of small intestine</t>
+    <t>résection partielle de l'intestin grêle</t>
   </si>
   <si>
     <t>57470004</t>
   </si>
   <si>
-    <t>Open reduction of fracture of femur with internal fixation</t>
+    <t>réduction ouverte d'une fracture du fémur avec fixation interne</t>
   </si>
   <si>
     <t>68432004</t>
   </si>
   <si>
-    <t>Open reduction of fracture of carpals and metacarpals with internal fixation</t>
+    <t>réduction ouverte de fracture du carpe et du métacarpe avec fixation interne</t>
   </si>
   <si>
     <t>73536002</t>
   </si>
   <si>
-    <t>Myotomy of colon</t>
+    <t>myotomie du côlon</t>
   </si>
   <si>
     <t>74011006</t>
   </si>
   <si>
-    <t>Open reduction of fracture of tibia and fibula with internal fixation</t>
+    <t>réduction ouverte d'une fracture du tibia et de la fibula avec ostéosynthèse interne</t>
   </si>
   <si>
     <t>74406002</t>
   </si>
   <si>
-    <t>Open heart valvuloplasty of mitral valve without replacement</t>
+    <t>valvuloplastie de la valve mitrale à cœur ouvert sans remplacement</t>
   </si>
   <si>
     <t>75835007</t>
   </si>
   <si>
-    <t>Laparoscopic-assisted vaginal hysterectomy</t>
+    <t>hystérectomie vaginale par laparoscopie</t>
   </si>
   <si>
     <t>76876009</t>
   </si>
   <si>
-    <t>Bilateral oophorectomy</t>
+    <t>ovariectomie bilatérale</t>
   </si>
   <si>
     <t>79544006</t>
   </si>
   <si>
-    <t>Complete axillary lymphadenectomy</t>
+    <t>lymphadénectomie axillaire complète</t>
   </si>
   <si>
     <t>89522007</t>
   </si>
   <si>
-    <t>Colocolostomy</t>
+    <t>colocolostomie</t>
   </si>
   <si>
     <t>112892003</t>
   </si>
   <si>
-    <t>Radical excision of iliac lymph nodes</t>
+    <t>exérèse de nœuds lymphatiques iliaques</t>
   </si>
   <si>
     <t>112925006</t>
   </si>
   <si>
-    <t>Repair of obstetric laceration of vulva</t>
+    <t>réparation de déchirure obstétricale vulvaire</t>
   </si>
   <si>
     <t>171841007</t>
   </si>
   <si>
-    <t>Endoscopic carpal tunnel release</t>
+    <t>libération endoscopique du canal carpien</t>
   </si>
   <si>
     <t>172555009</t>
   </si>
   <si>
-    <t>Anterior vitrectomy</t>
+    <t>vitrectomie antérieure</t>
   </si>
   <si>
     <t>172571009</t>
   </si>
   <si>
-    <t>Epiretinal dissection</t>
+    <t>dissection de membrane épirétinienne</t>
   </si>
   <si>
     <t>175907006</t>
   </si>
   <si>
-    <t>Nephroureterectomy</t>
+    <t>néphro-urétérectomie</t>
   </si>
   <si>
     <t>176258007</t>
   </si>
   <si>
-    <t>Open prostatectomy</t>
+    <t>prostatectomie par voie ouverte</t>
   </si>
   <si>
     <t>176820000</t>
   </si>
   <si>
-    <t>Curettage of uterus</t>
-  </si>
-  <si>
-    <t>232834008</t>
-  </si>
-  <si>
-    <t>Balloon aortic valvotomy</t>
+    <t>curetage de l'utérus</t>
   </si>
   <si>
     <t>265160007</t>
   </si>
   <si>
-    <t>Total prosthetic replacement of hip joint not using cement</t>
+    <t>arthroplastie totale de la hanche non cimentée</t>
   </si>
   <si>
     <t>272300006</t>
   </si>
   <si>
-    <t>Closed reduction of fracture of femur with internal fixation</t>
+    <t>réduction fermée de fracture du fémur avec fixation interne</t>
   </si>
   <si>
     <t>276861004</t>
   </si>
   <si>
-    <t>Percutaneous balloon angioplasty of artery</t>
+    <t>angioplastie percutanée au ballonnet d'une artère</t>
   </si>
   <si>
     <t>287708003</t>
   </si>
   <si>
-    <t>Transurethral bladder excision</t>
+    <t>résection transurétrale de vessie</t>
   </si>
   <si>
     <t>304039000</t>
   </si>
   <si>
-    <t>Skin flap operation</t>
+    <t>intervention chirurgicale d'un lambeau de peau</t>
   </si>
   <si>
     <t>315059002</t>
   </si>
   <si>
-    <t>Laparoscopic salpingectomy</t>
+    <t>salpingectomie par laparoscopie</t>
   </si>
   <si>
     <t>384676001</t>
   </si>
   <si>
-    <t>Operation on mouth</t>
+    <t>intervention chirurgicale sur la bouche</t>
   </si>
   <si>
     <t>386649003</t>
   </si>
   <si>
-    <t>Partial hip replacement by prosthesis</t>
+    <t>remplacement partiel d'une hanche par une prothèse</t>
   </si>
   <si>
     <t>386792000</t>
   </si>
   <si>
-    <t>Transurethral resection of bladder neoplasm</t>
+    <t>résection transurétrale d'une tumeur de la vessie</t>
   </si>
   <si>
     <t>391897002</t>
   </si>
   <si>
-    <t>Aspiration curettage of uterus for termination of pregnancy</t>
+    <t>curetage utérin par aspiration pour interruption de grossesse</t>
   </si>
   <si>
     <t>425767004</t>
   </si>
   <si>
-    <t>Implantation of radioactive seed into prostate</t>
+    <t>implantation de grain radioactif dans la prostate</t>
   </si>
   <si>
     <t>431316002</t>
   </si>
   <si>
-    <t>Laparoscopic subtotal hysterectomy</t>
+    <t>hystérectomie subtotale laparoscopique</t>
   </si>
   <si>
     <t>448808006</t>
   </si>
   <si>
-    <t>Fusion of cervicothoracic region of spine by anterior approach</t>
+    <t>arthrodèse cervicale antérieure</t>
   </si>
   <si>
     <t>448942003</t>
   </si>
   <si>
-    <t>Fusion of lumbosacral region of spine by posterior approach</t>
+    <t>arthrodèse lombosacrée postérieure</t>
   </si>
   <si>
     <t>448943008</t>
   </si>
   <si>
-    <t>Fusion of thoracolumbar region of spine by anterior approach</t>
+    <t>arthrodèse thoracolombaire antérieure</t>
   </si>
   <si>
     <t>448944002</t>
   </si>
   <si>
-    <t>Fusion of thoracolumbar region of spine by posterior approach</t>
+    <t>arthrodèse thoracolombaire postérieure</t>
   </si>
   <si>
     <t>449048009</t>
   </si>
   <si>
-    <t>Fusion of lumbosacral region of spine by anterior approach</t>
+    <t>arthrodèse lombosacrée antérieure</t>
   </si>
   <si>
     <t>449320003</t>
   </si>
   <si>
-    <t>Ligation and stripping of varicose vein of lower limb</t>
+    <t>ligature et éveinage de varice du membre inférieur</t>
   </si>
   <si>
     <t>608785007</t>
   </si>
   <si>
-    <t>Open reduction of fracture of radius and ulna with internal fixation</t>
+    <t>réduction ouverte de fracture de radius et ulna avec ostéosynthèse interne</t>
   </si>
   <si>
     <t>609230000</t>
   </si>
   <si>
-    <t>Laparoscopic bilateral salpingo-oophorectomy</t>
+    <t>salpingo-ovariectomie bilatérale laparoscopique</t>
   </si>
   <si>
     <t>708614008</t>
   </si>
   <si>
-    <t>Laparoscopic lysis of adhesion of peritoneum</t>
+    <t>adhésiolyse laparoscopique d'adhérence péritonéale</t>
   </si>
   <si>
     <t>708651002</t>
   </si>
   <si>
-    <t>Partial excision of vertebra</t>
+    <t>résection vertébrale partielle</t>
   </si>
   <si>
     <t>708983005</t>
   </si>
   <si>
-    <t>Laparoscopic bypass of stomach</t>
+    <t>court-circuit gastrique par laparoscopie</t>
   </si>
   <si>
     <t>709013008</t>
   </si>
   <si>
-    <t>Removal of implant device from bone</t>
+    <t>retrait de dispositif implantable osseux</t>
   </si>
   <si>
     <t>710785000</t>
   </si>
   <si>
-    <t>Laparoscopic repair of hernia</t>
+    <t>réparation laparoscopique de hernie</t>
   </si>
   <si>
     <t>737067005</t>
   </si>
   <si>
-    <t>Repair of ventral hernia using graft</t>
+    <t>cure de hernie ventrale avec greffe</t>
   </si>
   <si>
     <t>771626001</t>
   </si>
   <si>
-    <t>Open repair of femoral hernia using sutures</t>
+    <t>cure de hernie fémorale par voie ouverte avec sutures</t>
   </si>
   <si>
     <t>771663005</t>
   </si>
   <si>
-    <t>Open repair of umbilical hernia using sutures</t>
+    <t>cure de hernie ombilicale par voie ouverte avec sutures</t>
   </si>
   <si>
     <t>771713005</t>
   </si>
   <si>
-    <t>Open repair of inguinal hernia using sutures</t>
+    <t>cure de hernie inguinale par voie ouverte avec sutures</t>
   </si>
   <si>
     <t>771719009</t>
   </si>
   <si>
-    <t>Open repair of epigastric hernia using sutures</t>
+    <t>cure de hernie épigastrique par voie ouverte avec sutures</t>
   </si>
   <si>
     <t>788180009</t>
   </si>
   <si>
-    <t>Lower uterine segment cesarean section</t>
+    <t>césarienne avec hystérotomie du segment inférieur de l'utérus</t>
   </si>
   <si>
     <t>860930005</t>
   </si>
   <si>
-    <t>Surgery of cataract of left eye</t>
+    <t>chirurgie de la cataracte de l'œil gauche</t>
   </si>
   <si>
     <t>860934001</t>
   </si>
   <si>
-    <t>Surgery of cataract of right eye</t>
+    <t>chirurgie de la cataracte de l'œil droit</t>
   </si>
   <si>
     <t>1144279009</t>
   </si>
   <si>
-    <t>Fitting of complete denture</t>
+    <t>ajustement de prothèse dentaire complète</t>
   </si>
   <si>
     <t>871898007</t>
   </si>
   <si>
-    <t>Administration of live attenuated Human alphaherpesvirus 3 vaccine</t>
+    <t>administration de produit contenant seulement vaccin vivant atténué contre alphaherpèsvirus humain de type 3</t>
   </si>
   <si>
     <t>840534001</t>
   </si>
   <si>
-    <t>Administration of SARS-CoV-2 antigen vaccine</t>
+    <t>vaccination par antigène du SARS-CoV-2</t>
   </si>
   <si>
     <t>746051007</t>
   </si>
   <si>
-    <t>Endovascular insertion of drug coated stent</t>
+    <t>implantation endovasculaire d'un stent actif</t>
   </si>
   <si>
     <t>445982009</t>
   </si>
   <si>
-    <t>Endoscopy and biopsy of upper gastrointestinal tract</t>
+    <t>endoscopie et biopsie du tractus digestif supérieur</t>
   </si>
   <si>
     <t>445563009</t>
   </si>
   <si>
-    <t>Counseling for sexually transmitted disease</t>
+    <t>conseil sur les IST (infection sexuellement transmissible)</t>
   </si>
   <si>
     <t>444822002</t>
   </si>
   <si>
-    <t>Screening for malignant neoplasm of prostate</t>
+    <t>dépistage d'un néoplasme malin de la prostate</t>
   </si>
   <si>
     <t>444813003</t>
   </si>
   <si>
-    <t>Prophylactic immunotherapy</t>
+    <t>immunothérapie prophylactique</t>
   </si>
   <si>
     <t>444783004</t>
   </si>
   <si>
-    <t>Screening colonoscopy</t>
+    <t>coloscopie de dépistage</t>
   </si>
   <si>
     <t>444733009</t>
   </si>
   <si>
-    <t>Preoperative cardiovascular examination</t>
+    <t>examen cardiovasculaire préopératoire</t>
   </si>
   <si>
     <t>444638005</t>
   </si>
   <si>
-    <t>Screening for malignant neoplasm of skin</t>
+    <t>dépistage d'un néoplasme malin cutané</t>
   </si>
   <si>
     <t>444598000</t>
   </si>
   <si>
-    <t>Pretransplant evaluation of donor</t>
+    <t>bilan prétransplantation de donneur de rein</t>
   </si>
   <si>
     <t>444562008</t>
   </si>
   <si>
-    <t>Preoperative pulmonary examination</t>
+    <t>examen pulmonaire préopératoire</t>
   </si>
   <si>
     <t>442460002</t>
   </si>
   <si>
-    <t>Procedure on wound</t>
+    <t>procédure sur une plaie</t>
   </si>
   <si>
     <t>442309004</t>
   </si>
   <si>
-    <t>Insertion of tunnelled venous catheter</t>
+    <t>insertion d'un cathéter veineux tunnelisé</t>
   </si>
   <si>
     <t>439740005</t>
   </si>
   <si>
-    <t>Postoperative follow-up visit</t>
+    <t>visite de suivi postopératoire</t>
   </si>
   <si>
     <t>433233004</t>
   </si>
   <si>
-    <t>Exercise stress echocardiography</t>
+    <t>échocardiographie à l'effort</t>
   </si>
   <si>
     <t>428817001</t>
   </si>
   <si>
-    <t>Insertion of stent into ureter</t>
+    <t>insertion d'un stent dans l'uretère</t>
   </si>
   <si>
     <t>427247008</t>
   </si>
   <si>
-    <t>Hearing assessment</t>
+    <t>bilan auditif</t>
   </si>
   <si>
     <t>426931009</t>
   </si>
   <si>
-    <t>Subacute bacterial endocarditis prophylaxis</t>
+    <t>prophylaxie d'endocardite bactérienne subaigüe</t>
   </si>
   <si>
     <t>425983008</t>
   </si>
   <si>
-    <t>Autologous peripheral blood stem cell transplant</t>
+    <t>autogreffe de cellules souches périphériques</t>
   </si>
   <si>
     <t>425934009</t>
   </si>
   <si>
-    <t>Cardioverter defibrillator procedure</t>
+    <t>cardioversion avec défibrillateur</t>
   </si>
   <si>
     <t>425843001</t>
   </si>
   <si>
-    <t>Allogeneic peripheral blood stem cell transplant</t>
+    <t>greffe allogénique de cellules souches périphériques</t>
   </si>
   <si>
     <t>425196008</t>
   </si>
   <si>
-    <t>Insertion of peripherally inserted central catheter</t>
+    <t>insertion d'un CCIVP (cathéter central introduit par voie périphérique)</t>
   </si>
   <si>
     <t>424294008</t>
   </si>
   <si>
-    <t>Delayed hypersensitivity skin test for tuberculin PPD</t>
+    <t>test cutané d'hypersensibilité retardée au dérivé protéinique purifié de tuberculine</t>
   </si>
   <si>
     <t>424225000</t>
   </si>
   <si>
-    <t>Cardiovascular stress test using the dobutamine stress test protocol</t>
+    <t>test d'effort cardiovasculaire sous perfusion de dobutamine</t>
   </si>
   <si>
     <t>420171008</t>
   </si>
   <si>
-    <t>Fluoroscopic angiography of carotid artery with contrast</t>
+    <t>artériographie carotidienne guidée par fluoroscopie avec produit de contraste</t>
   </si>
   <si>
     <t>413467001</t>
   </si>
   <si>
-    <t>Aftercare</t>
+    <t>suivi</t>
   </si>
   <si>
     <t>413107006</t>
   </si>
   <si>
-    <t>Hepatitis C screening</t>
+    <t>dépistage de l'hépatite C</t>
   </si>
   <si>
     <t>410624000</t>
   </si>
   <si>
-    <t>Well child visit, 2 month</t>
+    <t>consultation d'enfant bien portant : 2 mois</t>
   </si>
   <si>
     <t>410620009</t>
   </si>
   <si>
-    <t>Well child visit</t>
+    <t>consultation d'enfant bien portant</t>
   </si>
   <si>
     <t>410321003</t>
   </si>
   <si>
-    <t>Wellness health education, guidance, and counselling</t>
+    <t>enseignement, directives et counseling relatifs au bien-être en matière de santé</t>
   </si>
   <si>
     <t>410290005</t>
   </si>
   <si>
-    <t>Family planning education, guidance, and counseling</t>
+    <t>enseignement, directives et counseling relatifs à la planification familiale</t>
   </si>
   <si>
     <t>410289001</t>
   </si>
   <si>
-    <t>Exercises education, guidance, and counselling</t>
+    <t>enseignement, directives et counseling relatifs aux exercices</t>
   </si>
   <si>
     <t>410279000</t>
@@ -5448,6 +5442,12 @@
     <t>Palliative care</t>
   </si>
   <si>
+    <t>103716009</t>
+  </si>
+  <si>
+    <t>Placement of stent</t>
+  </si>
+  <si>
     <t>1296925008</t>
   </si>
   <si>
@@ -6042,7 +6042,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>urn:oid:2.16.840.1.113883.6.96</t>
+    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -6298,7 +6298,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B994"/>
+  <dimension ref="A1:B995"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -11563,2697 +11563,2705 @@
     </row>
     <row r="658">
       <c r="A658" t="s" s="2">
-        <v>1337</v>
+        <v>63</v>
       </c>
       <c r="B658" t="s" s="2">
-        <v>1338</v>
+        <v>64</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="s" s="2">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="B659" t="s" s="2">
-        <v>1340</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="s" s="2">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B660" t="s" s="2">
-        <v>1342</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="s" s="2">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="B661" t="s" s="2">
-        <v>1344</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="s" s="2">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="B662" t="s" s="2">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="s" s="2">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="B663" t="s" s="2">
-        <v>1348</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="s" s="2">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="B664" t="s" s="2">
-        <v>1350</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="s" s="2">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="B665" t="s" s="2">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="s" s="2">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="B666" t="s" s="2">
-        <v>1354</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="s" s="2">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B667" t="s" s="2">
-        <v>1356</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="s" s="2">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B668" t="s" s="2">
-        <v>1358</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="s" s="2">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B669" t="s" s="2">
-        <v>1360</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="s" s="2">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B670" t="s" s="2">
-        <v>1362</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="s" s="2">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B671" t="s" s="2">
-        <v>1364</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="s" s="2">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B672" t="s" s="2">
-        <v>1366</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="s" s="2">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="B673" t="s" s="2">
-        <v>1368</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="s" s="2">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="B674" t="s" s="2">
-        <v>1370</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="s" s="2">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B675" t="s" s="2">
-        <v>1372</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="s" s="2">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="B676" t="s" s="2">
-        <v>1374</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="s" s="2">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B677" t="s" s="2">
-        <v>1376</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="s" s="2">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="B678" t="s" s="2">
-        <v>1378</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="s" s="2">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="B679" t="s" s="2">
-        <v>1380</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="s" s="2">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="B680" t="s" s="2">
-        <v>1382</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="s" s="2">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="B681" t="s" s="2">
-        <v>1384</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="s" s="2">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B682" t="s" s="2">
-        <v>1386</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="s" s="2">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B683" t="s" s="2">
-        <v>1388</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="s" s="2">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="B684" t="s" s="2">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="s" s="2">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="B685" t="s" s="2">
-        <v>1392</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="s" s="2">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="B686" t="s" s="2">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="s" s="2">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="B687" t="s" s="2">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="s" s="2">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="B688" t="s" s="2">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="s" s="2">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="B689" t="s" s="2">
-        <v>1400</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="s" s="2">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="B690" t="s" s="2">
-        <v>1402</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="B691" t="s" s="2">
-        <v>1404</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="B692" t="s" s="2">
-        <v>1406</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="B693" t="s" s="2">
-        <v>1408</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="B694" t="s" s="2">
-        <v>1410</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="B695" t="s" s="2">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="B696" t="s" s="2">
-        <v>1414</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="B697" t="s" s="2">
-        <v>1416</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="B698" t="s" s="2">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="B699" t="s" s="2">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="B700" t="s" s="2">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="B701" t="s" s="2">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="B702" t="s" s="2">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="B703" t="s" s="2">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="B704" t="s" s="2">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="B705" t="s" s="2">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="B706" t="s" s="2">
-        <v>1434</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="B707" t="s" s="2">
-        <v>1436</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B708" t="s" s="2">
-        <v>1438</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="B709" t="s" s="2">
-        <v>1440</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="B710" t="s" s="2">
-        <v>1442</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B717" t="s" s="2">
-        <v>1456</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B718" t="s" s="2">
-        <v>1458</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="B719" t="s" s="2">
-        <v>1460</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="B720" t="s" s="2">
-        <v>1462</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B721" t="s" s="2">
-        <v>1464</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="B722" t="s" s="2">
-        <v>1466</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="B723" t="s" s="2">
-        <v>1468</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="B724" t="s" s="2">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="B725" t="s" s="2">
-        <v>1472</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="B726" t="s" s="2">
-        <v>1474</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="B727" t="s" s="2">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="B728" t="s" s="2">
-        <v>1478</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="B729" t="s" s="2">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="s" s="2">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="B730" t="s" s="2">
-        <v>1482</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="s" s="2">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="B731" t="s" s="2">
-        <v>1484</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="s" s="2">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="B732" t="s" s="2">
-        <v>1486</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="s" s="2">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B733" t="s" s="2">
-        <v>1488</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="s" s="2">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="B734" t="s" s="2">
-        <v>1490</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="s" s="2">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B735" t="s" s="2">
-        <v>1492</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="s" s="2">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B736" t="s" s="2">
-        <v>1494</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="s" s="2">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="B737" t="s" s="2">
-        <v>1496</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="s" s="2">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="s" s="2">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="B739" t="s" s="2">
-        <v>1500</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="s" s="2">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B740" t="s" s="2">
-        <v>1502</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="s" s="2">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="B741" t="s" s="2">
-        <v>1504</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="s" s="2">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="B742" t="s" s="2">
-        <v>1506</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="s" s="2">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="B743" t="s" s="2">
-        <v>1508</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="s" s="2">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="B744" t="s" s="2">
-        <v>1510</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="s" s="2">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="B745" t="s" s="2">
-        <v>1512</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="s" s="2">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="B746" t="s" s="2">
-        <v>1514</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="s" s="2">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="B747" t="s" s="2">
-        <v>1516</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="s" s="2">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="B748" t="s" s="2">
-        <v>1518</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="s" s="2">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="B749" t="s" s="2">
-        <v>1520</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="s" s="2">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="B750" t="s" s="2">
-        <v>1522</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="s" s="2">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="B751" t="s" s="2">
-        <v>1524</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="s" s="2">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="B752" t="s" s="2">
-        <v>1526</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="s" s="2">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="B753" t="s" s="2">
-        <v>1528</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="s" s="2">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="B754" t="s" s="2">
-        <v>1530</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="s" s="2">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="B755" t="s" s="2">
-        <v>1532</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="s" s="2">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="B756" t="s" s="2">
-        <v>1534</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="s" s="2">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="B757" t="s" s="2">
-        <v>1536</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="s" s="2">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="B758" t="s" s="2">
-        <v>1538</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="s" s="2">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="B759" t="s" s="2">
-        <v>1540</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="s" s="2">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="B760" t="s" s="2">
-        <v>1542</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="s" s="2">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="B761" t="s" s="2">
-        <v>1544</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="s" s="2">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="B762" t="s" s="2">
-        <v>1546</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="s" s="2">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="B763" t="s" s="2">
-        <v>1548</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="s" s="2">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="B764" t="s" s="2">
-        <v>1550</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="s" s="2">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="B765" t="s" s="2">
-        <v>1552</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="s" s="2">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="B766" t="s" s="2">
-        <v>1554</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="s" s="2">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="B767" t="s" s="2">
-        <v>1556</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="s" s="2">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="B768" t="s" s="2">
-        <v>1558</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="s" s="2">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="B769" t="s" s="2">
-        <v>1560</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="s" s="2">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="B770" t="s" s="2">
-        <v>1562</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="s" s="2">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="B771" t="s" s="2">
-        <v>1564</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="s" s="2">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="B772" t="s" s="2">
-        <v>1566</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="s" s="2">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="B773" t="s" s="2">
-        <v>1568</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="s" s="2">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="B774" t="s" s="2">
-        <v>1570</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="s" s="2">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="B775" t="s" s="2">
-        <v>1572</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="s" s="2">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="B776" t="s" s="2">
-        <v>1574</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="s" s="2">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="B777" t="s" s="2">
-        <v>1576</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="s" s="2">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="B778" t="s" s="2">
-        <v>1578</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="s" s="2">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="B779" t="s" s="2">
-        <v>1580</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="s" s="2">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="B780" t="s" s="2">
-        <v>1582</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="s" s="2">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="B781" t="s" s="2">
-        <v>1584</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="s" s="2">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="B782" t="s" s="2">
-        <v>1586</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="s" s="2">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="B783" t="s" s="2">
-        <v>1588</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="s" s="2">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="B784" t="s" s="2">
-        <v>1590</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="s" s="2">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="B785" t="s" s="2">
-        <v>1592</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="s" s="2">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="B786" t="s" s="2">
-        <v>1594</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="s" s="2">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="B787" t="s" s="2">
-        <v>1596</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="s" s="2">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="B788" t="s" s="2">
-        <v>1598</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="s" s="2">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="B789" t="s" s="2">
-        <v>1600</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="s" s="2">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="B790" t="s" s="2">
-        <v>1602</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="s" s="2">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="B791" t="s" s="2">
-        <v>1604</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="s" s="2">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="B792" t="s" s="2">
-        <v>1606</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="s" s="2">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="B793" t="s" s="2">
-        <v>1608</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="s" s="2">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="B794" t="s" s="2">
-        <v>1610</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="s" s="2">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="B795" t="s" s="2">
-        <v>1612</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="s" s="2">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="B796" t="s" s="2">
-        <v>1614</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="s" s="2">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="B797" t="s" s="2">
-        <v>1616</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="s" s="2">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="B798" t="s" s="2">
-        <v>1618</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="s" s="2">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="B799" t="s" s="2">
-        <v>1620</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="s" s="2">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="B800" t="s" s="2">
-        <v>1622</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="s" s="2">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="B801" t="s" s="2">
-        <v>1624</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="s" s="2">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="B802" t="s" s="2">
-        <v>1626</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="s" s="2">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="B803" t="s" s="2">
-        <v>1628</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="s" s="2">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="B804" t="s" s="2">
-        <v>1630</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="s" s="2">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="B805" t="s" s="2">
-        <v>1632</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="s" s="2">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="B806" t="s" s="2">
-        <v>1634</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="s" s="2">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="B807" t="s" s="2">
-        <v>1636</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="s" s="2">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="B808" t="s" s="2">
-        <v>1638</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="s" s="2">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="B809" t="s" s="2">
-        <v>1640</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="s" s="2">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="B810" t="s" s="2">
-        <v>1642</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="s" s="2">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="B811" t="s" s="2">
-        <v>1644</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="s" s="2">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="B812" t="s" s="2">
-        <v>1646</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="s" s="2">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="B813" t="s" s="2">
-        <v>1648</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="s" s="2">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="B814" t="s" s="2">
-        <v>1650</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="s" s="2">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="B815" t="s" s="2">
-        <v>1652</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="s" s="2">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="B816" t="s" s="2">
-        <v>1654</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="s" s="2">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="B817" t="s" s="2">
-        <v>1656</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="s" s="2">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="B818" t="s" s="2">
-        <v>1658</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="s" s="2">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="B819" t="s" s="2">
-        <v>1660</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="s" s="2">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="B820" t="s" s="2">
-        <v>1662</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="s" s="2">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="B821" t="s" s="2">
-        <v>1664</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="s" s="2">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="B822" t="s" s="2">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="s" s="2">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="B823" t="s" s="2">
-        <v>1668</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="s" s="2">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="B824" t="s" s="2">
-        <v>1670</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="s" s="2">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="B825" t="s" s="2">
-        <v>1672</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="B826" t="s" s="2">
-        <v>1674</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="s" s="2">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="B827" t="s" s="2">
-        <v>1676</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="s" s="2">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="B828" t="s" s="2">
-        <v>1678</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="s" s="2">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="B829" t="s" s="2">
-        <v>1680</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="s" s="2">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="B830" t="s" s="2">
-        <v>1682</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="s" s="2">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="B831" t="s" s="2">
-        <v>1684</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="s" s="2">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="B832" t="s" s="2">
-        <v>1686</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="s" s="2">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="B833" t="s" s="2">
-        <v>1688</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="s" s="2">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="B834" t="s" s="2">
-        <v>1690</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="s" s="2">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="B835" t="s" s="2">
-        <v>1692</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="s" s="2">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="B836" t="s" s="2">
-        <v>1694</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="s" s="2">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="B837" t="s" s="2">
-        <v>1696</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="s" s="2">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="B838" t="s" s="2">
-        <v>1698</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="s" s="2">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="B839" t="s" s="2">
-        <v>1700</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="s" s="2">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="B840" t="s" s="2">
-        <v>1702</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="s" s="2">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="B841" t="s" s="2">
-        <v>1704</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="s" s="2">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="B842" t="s" s="2">
-        <v>1706</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="s" s="2">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="B843" t="s" s="2">
-        <v>1708</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="s" s="2">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="B844" t="s" s="2">
-        <v>1710</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="s" s="2">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="B845" t="s" s="2">
-        <v>1712</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="s" s="2">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="B846" t="s" s="2">
-        <v>1714</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="s" s="2">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B847" t="s" s="2">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="s" s="2">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="B848" t="s" s="2">
-        <v>1718</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="s" s="2">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="B849" t="s" s="2">
-        <v>1720</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="s" s="2">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="B850" t="s" s="2">
-        <v>1722</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="s" s="2">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="B851" t="s" s="2">
-        <v>1724</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="s" s="2">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="B852" t="s" s="2">
-        <v>1726</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="s" s="2">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="B853" t="s" s="2">
-        <v>1728</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="s" s="2">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="B854" t="s" s="2">
-        <v>1730</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="s" s="2">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="B855" t="s" s="2">
-        <v>1732</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="s" s="2">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="B856" t="s" s="2">
-        <v>1734</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="s" s="2">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="B857" t="s" s="2">
-        <v>1736</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="s" s="2">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="B858" t="s" s="2">
-        <v>1738</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="s" s="2">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="B859" t="s" s="2">
-        <v>1740</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="s" s="2">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="B860" t="s" s="2">
-        <v>1742</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="s" s="2">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="B861" t="s" s="2">
-        <v>1744</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="s" s="2">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="B862" t="s" s="2">
-        <v>1746</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="s" s="2">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B863" t="s" s="2">
-        <v>1748</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="s" s="2">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="B864" t="s" s="2">
-        <v>1750</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="s" s="2">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="B865" t="s" s="2">
-        <v>1752</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="s" s="2">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="B866" t="s" s="2">
-        <v>1754</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="s" s="2">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="B867" t="s" s="2">
-        <v>1756</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="s" s="2">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="B868" t="s" s="2">
-        <v>1758</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="s" s="2">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="B869" t="s" s="2">
-        <v>1760</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="s" s="2">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="B870" t="s" s="2">
-        <v>1762</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="s" s="2">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="B871" t="s" s="2">
-        <v>1764</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="s" s="2">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="B872" t="s" s="2">
-        <v>1766</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="s" s="2">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="B873" t="s" s="2">
-        <v>1768</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="s" s="2">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="B874" t="s" s="2">
-        <v>1770</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="s" s="2">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="B875" t="s" s="2">
-        <v>1772</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="s" s="2">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="B876" t="s" s="2">
-        <v>1774</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="s" s="2">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="B877" t="s" s="2">
-        <v>1776</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="s" s="2">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="B878" t="s" s="2">
-        <v>1778</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="s" s="2">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="B879" t="s" s="2">
-        <v>1780</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="s" s="2">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="B880" t="s" s="2">
-        <v>1782</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="s" s="2">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="B881" t="s" s="2">
-        <v>1784</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="s" s="2">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="B882" t="s" s="2">
-        <v>1786</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="s" s="2">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="B883" t="s" s="2">
-        <v>1788</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="s" s="2">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="B884" t="s" s="2">
-        <v>1790</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="s" s="2">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="B885" t="s" s="2">
-        <v>1792</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="s" s="2">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="B886" t="s" s="2">
-        <v>1794</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="s" s="2">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="B887" t="s" s="2">
-        <v>1796</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="s" s="2">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="B888" t="s" s="2">
-        <v>1798</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="s" s="2">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="B889" t="s" s="2">
-        <v>1800</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="s" s="2">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="B890" t="s" s="2">
-        <v>1802</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="s" s="2">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="B891" t="s" s="2">
-        <v>1804</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="s" s="2">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="B892" t="s" s="2">
-        <v>1806</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="s" s="2">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="B893" t="s" s="2">
-        <v>1808</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="s" s="2">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="B894" t="s" s="2">
-        <v>1810</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="s" s="2">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="B895" t="s" s="2">
-        <v>1812</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="s" s="2">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="B896" t="s" s="2">
-        <v>1814</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="s" s="2">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="B897" t="s" s="2">
-        <v>1816</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="s" s="2">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="B898" t="s" s="2">
-        <v>1818</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="s" s="2">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="B899" t="s" s="2">
-        <v>1820</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="s" s="2">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="B900" t="s" s="2">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="s" s="2">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="B901" t="s" s="2">
-        <v>1824</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="s" s="2">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="B902" t="s" s="2">
-        <v>1826</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="s" s="2">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="B903" t="s" s="2">
-        <v>1828</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="s" s="2">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="B904" t="s" s="2">
-        <v>1830</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="s" s="2">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="B905" t="s" s="2">
-        <v>1832</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="s" s="2">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="B906" t="s" s="2">
-        <v>1834</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="s" s="2">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="B907" t="s" s="2">
-        <v>1836</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="s" s="2">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="B908" t="s" s="2">
-        <v>1838</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="s" s="2">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="B909" t="s" s="2">
-        <v>1840</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="s" s="2">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="B910" t="s" s="2">
-        <v>1842</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="s" s="2">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="B911" t="s" s="2">
-        <v>1844</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="s" s="2">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="B912" t="s" s="2">
-        <v>1846</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="s" s="2">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="B913" t="s" s="2">
-        <v>1848</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="s" s="2">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="B914" t="s" s="2">
-        <v>1850</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="s" s="2">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="B915" t="s" s="2">
-        <v>1852</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="s" s="2">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="B916" t="s" s="2">
-        <v>1854</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="s" s="2">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="B917" t="s" s="2">
-        <v>1856</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="s" s="2">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="B918" t="s" s="2">
-        <v>1858</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="s" s="2">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="B919" t="s" s="2">
-        <v>1860</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="s" s="2">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="B920" t="s" s="2">
-        <v>1862</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="s" s="2">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="B921" t="s" s="2">
-        <v>1864</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="s" s="2">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="B922" t="s" s="2">
-        <v>1866</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="s" s="2">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="B923" t="s" s="2">
-        <v>1868</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="s" s="2">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="B924" t="s" s="2">
-        <v>1870</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="s" s="2">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="B925" t="s" s="2">
-        <v>1872</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="s" s="2">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="B926" t="s" s="2">
-        <v>1874</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="s" s="2">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="B927" t="s" s="2">
-        <v>1876</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="s" s="2">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="B928" t="s" s="2">
-        <v>1878</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="s" s="2">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="B929" t="s" s="2">
-        <v>1880</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="s" s="2">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="B930" t="s" s="2">
-        <v>1882</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="s" s="2">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="B931" t="s" s="2">
-        <v>1884</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="s" s="2">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="B932" t="s" s="2">
-        <v>1886</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="s" s="2">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="B933" t="s" s="2">
-        <v>1888</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="s" s="2">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="B934" t="s" s="2">
-        <v>1890</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="s" s="2">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="B935" t="s" s="2">
-        <v>1892</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="s" s="2">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="B936" t="s" s="2">
-        <v>1894</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="s" s="2">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="B937" t="s" s="2">
-        <v>1896</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="s" s="2">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="B938" t="s" s="2">
-        <v>1898</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="s" s="2">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="B939" t="s" s="2">
-        <v>1900</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="s" s="2">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="B940" t="s" s="2">
-        <v>1902</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="s" s="2">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="B941" t="s" s="2">
-        <v>1904</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="s" s="2">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="B942" t="s" s="2">
-        <v>1906</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="s" s="2">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="B943" t="s" s="2">
-        <v>1908</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="s" s="2">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="B944" t="s" s="2">
-        <v>1910</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="s" s="2">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="B945" t="s" s="2">
-        <v>1912</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="s" s="2">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="B946" t="s" s="2">
-        <v>1914</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="s" s="2">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="B947" t="s" s="2">
-        <v>1916</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="s" s="2">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="B948" t="s" s="2">
-        <v>1918</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="s" s="2">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="B949" t="s" s="2">
-        <v>1920</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="s" s="2">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="B950" t="s" s="2">
-        <v>1922</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="s" s="2">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="B951" t="s" s="2">
-        <v>1924</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="s" s="2">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="B952" t="s" s="2">
-        <v>1926</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="s" s="2">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="B953" t="s" s="2">
-        <v>1928</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="s" s="2">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="B954" t="s" s="2">
-        <v>1930</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="s" s="2">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="B955" t="s" s="2">
-        <v>1932</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="s" s="2">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="B956" t="s" s="2">
-        <v>1934</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="s" s="2">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="B957" t="s" s="2">
-        <v>1936</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="s" s="2">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="B958" t="s" s="2">
-        <v>1938</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="s" s="2">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="B959" t="s" s="2">
-        <v>1940</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="s" s="2">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="B960" t="s" s="2">
-        <v>1942</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="s" s="2">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="B961" t="s" s="2">
-        <v>1944</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="s" s="2">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="B962" t="s" s="2">
-        <v>1946</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="s" s="2">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="B963" t="s" s="2">
-        <v>1948</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="s" s="2">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="B964" t="s" s="2">
-        <v>1950</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="s" s="2">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="B965" t="s" s="2">
-        <v>1952</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="s" s="2">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="B966" t="s" s="2">
-        <v>1954</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="s" s="2">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="B967" t="s" s="2">
-        <v>1956</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="s" s="2">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="B968" t="s" s="2">
-        <v>1958</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="s" s="2">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="B969" t="s" s="2">
-        <v>1960</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="s" s="2">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="B970" t="s" s="2">
-        <v>1962</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="s" s="2">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="B971" t="s" s="2">
-        <v>1964</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="s" s="2">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="B972" t="s" s="2">
-        <v>1966</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="s" s="2">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="B973" t="s" s="2">
-        <v>1968</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="s" s="2">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="B974" t="s" s="2">
-        <v>1970</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="s" s="2">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="B975" t="s" s="2">
-        <v>1972</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="s" s="2">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="B976" t="s" s="2">
-        <v>1974</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="s" s="2">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="B977" t="s" s="2">
-        <v>1976</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="s" s="2">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="B978" t="s" s="2">
-        <v>1978</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="s" s="2">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="B979" t="s" s="2">
-        <v>1980</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="s" s="2">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="B980" t="s" s="2">
-        <v>1982</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="s" s="2">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="B981" t="s" s="2">
-        <v>1984</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="s" s="2">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="B982" t="s" s="2">
-        <v>1986</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="s" s="2">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="B983" t="s" s="2">
-        <v>1988</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="s" s="2">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="B984" t="s" s="2">
-        <v>1990</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="s" s="2">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="B985" t="s" s="2">
-        <v>1992</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="s" s="2">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="B986" t="s" s="2">
-        <v>1994</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="s" s="2">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="B987" t="s" s="2">
-        <v>1996</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="s" s="2">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="B988" t="s" s="2">
-        <v>1998</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="s" s="2">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="B989" t="s" s="2">
-        <v>2000</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="s" s="2">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="B990" t="s" s="2">
-        <v>2002</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="s" s="2">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="B991" t="s" s="2">
-        <v>2004</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="s" s="2">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B992" t="s" s="2">
-        <v>2006</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="s" s="2">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B993" t="s" s="2">
-        <v>2007</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="s" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B994" t="s" s="2">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="s" s="2">
         <v>2008</v>
       </c>
-      <c r="B994" t="s" s="2">
+      <c r="B995" t="s" s="2">
         <v>2009</v>
       </c>
     </row>
